--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sebamar-cotizador\backend\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\German\Documents\sebamarapp\backend\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1340FFE0-34BD-43AB-A1F4-52761D7A2D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11535" activeTab="4"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="939" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>
@@ -17,18 +18,30 @@
     <sheet name="RAJAS_HERRERO" sheetId="3" r:id="rId3"/>
     <sheet name="RAJAS_MODENA" sheetId="4" r:id="rId4"/>
     <sheet name="PUERTAS_HERRERO" sheetId="5" r:id="rId5"/>
+    <sheet name="MEDIA_PUERTA_HERRERO" sheetId="6" r:id="rId6"/>
+    <sheet name="PUERTAS_MODENA" sheetId="7" r:id="rId7"/>
+    <sheet name="PUERTAS_ECO" sheetId="8" r:id="rId8"/>
+    <sheet name="POSTIGONES" sheetId="9" r:id="rId9"/>
+    <sheet name="PATAGONICAS_MODENA" sheetId="10" r:id="rId10"/>
+    <sheet name="MOSQUITEROS_VENTANA" sheetId="11" r:id="rId11"/>
+    <sheet name="PUERTAS_PLACA" sheetId="12" r:id="rId12"/>
+    <sheet name="SUPERFICIES" sheetId="13" r:id="rId13"/>
+    <sheet name="COLORES" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="260">
   <si>
     <t>MEDIDA</t>
   </si>
@@ -405,15 +418,9 @@
     <t>MODELO</t>
   </si>
   <si>
-    <t>SINVIDRIO</t>
-  </si>
-  <si>
     <t>MODELO 1</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>MODELO 1 VR</t>
   </si>
   <si>
@@ -435,9 +442,6 @@
     <t>MODELO 5</t>
   </si>
   <si>
-    <t>SI</t>
-  </si>
-  <si>
     <t>MODELO 6</t>
   </si>
   <si>
@@ -466,12 +470,363 @@
   </si>
   <si>
     <t>ADICIONALES</t>
+  </si>
+  <si>
+    <t>V/ENTERO</t>
+  </si>
+  <si>
+    <t>V/REPARTIDO</t>
+  </si>
+  <si>
+    <t>3/4 V ENTERO</t>
+  </si>
+  <si>
+    <t>3/4 V REPARTIDO</t>
+  </si>
+  <si>
+    <t>1/2 V ENTERO</t>
+  </si>
+  <si>
+    <t>1/2 V REPARTIDO</t>
+  </si>
+  <si>
+    <t>4 TRAVEZAÑOS</t>
+  </si>
+  <si>
+    <t>1 TRAVESAÑO</t>
+  </si>
+  <si>
+    <t>MODELO C/PANEL</t>
+  </si>
+  <si>
+    <t>MODELO 3VR</t>
+  </si>
+  <si>
+    <t>CORREDIZO</t>
+  </si>
+  <si>
+    <t>DE_ABRIR</t>
+  </si>
+  <si>
+    <t>HOJAS</t>
+  </si>
+  <si>
+    <t>120x90</t>
+  </si>
+  <si>
+    <t>150x90</t>
+  </si>
+  <si>
+    <t>180x90</t>
+  </si>
+  <si>
+    <t>200x90</t>
+  </si>
+  <si>
+    <t>220x90</t>
+  </si>
+  <si>
+    <t>240x90</t>
+  </si>
+  <si>
+    <t>200x110</t>
+  </si>
+  <si>
+    <t>220x110</t>
+  </si>
+  <si>
+    <t>240x110</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>VIDRIO_4MM</t>
+  </si>
+  <si>
+    <t>VIDRIO_3+3</t>
+  </si>
+  <si>
+    <t>1_RAJA</t>
+  </si>
+  <si>
+    <t>2_RAJA</t>
+  </si>
+  <si>
+    <t>120x50</t>
+  </si>
+  <si>
+    <t>150x50</t>
+  </si>
+  <si>
+    <t>180x50</t>
+  </si>
+  <si>
+    <t>200x50</t>
+  </si>
+  <si>
+    <t>220x80</t>
+  </si>
+  <si>
+    <t>240x80</t>
+  </si>
+  <si>
+    <t>120x130</t>
+  </si>
+  <si>
+    <t>150x130</t>
+  </si>
+  <si>
+    <t>180x130</t>
+  </si>
+  <si>
+    <t>200x130</t>
+  </si>
+  <si>
+    <t>220x130</t>
+  </si>
+  <si>
+    <t>240x130</t>
+  </si>
+  <si>
+    <t>120x180</t>
+  </si>
+  <si>
+    <t>150x180</t>
+  </si>
+  <si>
+    <t>180x180</t>
+  </si>
+  <si>
+    <t>200x180</t>
+  </si>
+  <si>
+    <t>220x180</t>
+  </si>
+  <si>
+    <t>240x180</t>
+  </si>
+  <si>
+    <t>MARCO_10</t>
+  </si>
+  <si>
+    <t>MARCO_15</t>
+  </si>
+  <si>
+    <t>ALUMINIO</t>
+  </si>
+  <si>
+    <t>PLACA</t>
+  </si>
+  <si>
+    <t>FINGER_PINO</t>
+  </si>
+  <si>
+    <t>060x200</t>
+  </si>
+  <si>
+    <t>070x200</t>
+  </si>
+  <si>
+    <t>080x200</t>
+  </si>
+  <si>
+    <t>PINO_CEDRO</t>
+  </si>
+  <si>
+    <t>CEDRO_CEDRO</t>
+  </si>
+  <si>
+    <t>ALUMINIO_PINO</t>
+  </si>
+  <si>
+    <t>ALUMINIO_CEDRO</t>
+  </si>
+  <si>
+    <t>EMBUTIR</t>
+  </si>
+  <si>
+    <t>FINGER_CEDRO</t>
+  </si>
+  <si>
+    <t>CATEGORIA</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>SUBITEM</t>
+  </si>
+  <si>
+    <t>VALOR</t>
+  </si>
+  <si>
+    <t>RECARGO</t>
+  </si>
+  <si>
+    <t>CUATRO_HOJAS</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>TRES_HOJAS</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>NATURAL</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>BRONCE</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>NEGRO</t>
+  </si>
+  <si>
+    <t>HERRAJE_BLANCO</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>SUPERFICIE</t>
+  </si>
+  <si>
+    <t>PANO_FIJO</t>
+  </si>
+  <si>
+    <t>HERRERO</t>
+  </si>
+  <si>
+    <t>MODENA</t>
+  </si>
+  <si>
+    <t>PREMARCO</t>
+  </si>
+  <si>
+    <t>CONTRAMARCO</t>
+  </si>
+  <si>
+    <t>TRAVESANO</t>
+  </si>
+  <si>
+    <t>PERFIL_ACOPLE</t>
+  </si>
+  <si>
+    <t>MOSQUITERO_FIJO</t>
+  </si>
+  <si>
+    <t>CAJON_BLOCK</t>
+  </si>
+  <si>
+    <t>CORTINAS</t>
+  </si>
+  <si>
+    <t>PVC</t>
+  </si>
+  <si>
+    <t>EXTRA</t>
+  </si>
+  <si>
+    <t>BIPUNTO</t>
+  </si>
+  <si>
+    <t>BIPUNTO_CON_LLAVE</t>
+  </si>
+  <si>
+    <t>OSCILOBATIENTE</t>
+  </si>
+  <si>
+    <t>CP8</t>
+  </si>
+  <si>
+    <t>VOLCABLE</t>
+  </si>
+  <si>
+    <t>BRAZO_DE_EMPUJE</t>
+  </si>
+  <si>
+    <t>CARTELPROHIBIDO</t>
+  </si>
+  <si>
+    <t>BARRAL</t>
+  </si>
+  <si>
+    <t>RECTO</t>
+  </si>
+  <si>
+    <t>CURVO</t>
+  </si>
+  <si>
+    <t>HERRAJE</t>
+  </si>
+  <si>
+    <t>PLEGADIZO</t>
+  </si>
+  <si>
+    <t>CORREDIZO_MAS_3</t>
+  </si>
+  <si>
+    <t>PLEGADIZO_MAS_3</t>
+  </si>
+  <si>
+    <t>BISAGRA_EXTRA</t>
+  </si>
+  <si>
+    <t>PICAPORTE</t>
+  </si>
+  <si>
+    <t>MEDIA_MANIJA</t>
+  </si>
+  <si>
+    <t>CERRADURA</t>
+  </si>
+  <si>
+    <t>PUERTA_MOSQUITERO</t>
+  </si>
+  <si>
+    <t>6MM</t>
+  </si>
+  <si>
+    <t>4+4</t>
+  </si>
+  <si>
+    <t>5+5</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>BLANCO</t>
+  </si>
+  <si>
+    <t>BRONCE COLONIAL</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>SIMIL MADERA</t>
+  </si>
+  <si>
+    <t>2.8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -785,14 +1140,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,7 +1164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,7 +1181,7 @@
         <v>2556</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -843,7 +1198,7 @@
         <v>3570</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -860,7 +1215,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -877,7 +1232,7 @@
         <v>5622</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -894,7 +1249,7 @@
         <v>7140</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -911,7 +1266,7 @@
         <v>8676</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -928,7 +1283,7 @@
         <v>9696</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -945,7 +1300,7 @@
         <v>4254</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -962,7 +1317,7 @@
         <v>5952</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -979,7 +1334,7 @@
         <v>7656</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -996,7 +1351,7 @@
         <v>9354</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1013,7 +1368,7 @@
         <v>11910</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1030,7 +1385,7 @@
         <v>14460</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1047,7 +1402,7 @@
         <v>16158</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1064,7 +1419,7 @@
         <v>10716</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1081,7 +1436,7 @@
         <v>13098</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1098,7 +1453,7 @@
         <v>16668</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1115,7 +1470,7 @@
         <v>20244</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1132,7 +1487,7 @@
         <v>22620</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -1149,7 +1504,7 @@
         <v>13776</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1166,7 +1521,7 @@
         <v>16842</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -1183,7 +1538,7 @@
         <v>21432</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1200,7 +1555,7 @@
         <v>26022</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1217,7 +1572,7 @@
         <v>29088</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1234,7 +1589,7 @@
         <v>32148</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -1251,7 +1606,7 @@
         <v>35208</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -1268,7 +1623,7 @@
         <v>15312</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -1285,7 +1640,7 @@
         <v>18708</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -1302,7 +1657,7 @@
         <v>23814</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1319,378 +1674,2565 @@
         <v>28920</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B35" s="1">
         <v>59233</v>
-      </c>
-      <c r="C32" s="1">
-        <v>20650</v>
-      </c>
-      <c r="D32" s="1">
-        <v>24998</v>
-      </c>
-      <c r="E32" s="1">
-        <v>16842</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="1">
-        <v>62714</v>
-      </c>
-      <c r="C33" s="1">
-        <v>20650</v>
-      </c>
-      <c r="D33" s="1">
-        <v>27418</v>
-      </c>
-      <c r="E33" s="1">
-        <v>20580</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="1">
-        <v>68494</v>
-      </c>
-      <c r="C34" s="1">
-        <v>20650</v>
-      </c>
-      <c r="D34" s="1">
-        <v>31046</v>
-      </c>
-      <c r="E34" s="1">
-        <v>26196</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="1">
-        <v>73158</v>
       </c>
       <c r="C35" s="1">
         <v>20650</v>
       </c>
       <c r="D35" s="1">
-        <v>34675</v>
+        <v>24998</v>
       </c>
       <c r="E35" s="1">
-        <v>31806</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16842</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>79937</v>
+        <v>62714</v>
       </c>
       <c r="C36" s="1">
         <v>20650</v>
       </c>
       <c r="D36" s="1">
-        <v>37094</v>
+        <v>27418</v>
       </c>
       <c r="E36" s="1">
-        <v>35550</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>20580</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>83467</v>
+        <v>68494</v>
       </c>
       <c r="C37" s="1">
         <v>20650</v>
       </c>
       <c r="D37" s="1">
-        <v>39514</v>
+        <v>31046</v>
       </c>
       <c r="E37" s="1">
-        <v>39294</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>26196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>85547</v>
+        <v>73158</v>
       </c>
       <c r="C38" s="1">
         <v>20650</v>
       </c>
       <c r="D38" s="1">
+        <v>34675</v>
+      </c>
+      <c r="E38" s="1">
+        <v>31806</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1">
+        <v>79937</v>
+      </c>
+      <c r="C39" s="1">
+        <v>20650</v>
+      </c>
+      <c r="D39" s="1">
+        <v>37094</v>
+      </c>
+      <c r="E39" s="1">
+        <v>35550</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1">
+        <v>83467</v>
+      </c>
+      <c r="C40" s="1">
+        <v>20650</v>
+      </c>
+      <c r="D40" s="1">
+        <v>39514</v>
+      </c>
+      <c r="E40" s="1">
+        <v>39294</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="1">
+        <v>85547</v>
+      </c>
+      <c r="C41" s="1">
+        <v>20650</v>
+      </c>
+      <c r="D41" s="1">
         <v>41933</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E41" s="1">
         <v>43038</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B42" s="1">
         <v>67529</v>
-      </c>
-      <c r="C39" s="1">
-        <v>25813</v>
-      </c>
-      <c r="D39" s="1">
-        <v>29904</v>
-      </c>
-      <c r="E39" s="1">
-        <v>21432</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="1">
-        <v>71011</v>
-      </c>
-      <c r="C40" s="1">
-        <v>25813</v>
-      </c>
-      <c r="D40" s="1">
-        <v>32659</v>
-      </c>
-      <c r="E40" s="1">
-        <v>26196</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="1">
-        <v>76790</v>
-      </c>
-      <c r="C41" s="1">
-        <v>25813</v>
-      </c>
-      <c r="D41" s="1">
-        <v>36792</v>
-      </c>
-      <c r="E41" s="1">
-        <v>33336</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="1">
-        <v>80340</v>
       </c>
       <c r="C42" s="1">
         <v>25813</v>
       </c>
       <c r="D42" s="1">
-        <v>40925</v>
+        <v>29904</v>
       </c>
       <c r="E42" s="1">
-        <v>40482</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21432</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>87942</v>
+        <v>71011</v>
       </c>
       <c r="C43" s="1">
         <v>25813</v>
       </c>
       <c r="D43" s="1">
-        <v>43680</v>
+        <v>32659</v>
       </c>
       <c r="E43" s="1">
-        <v>45246</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>26196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>90649</v>
+        <v>76790</v>
       </c>
       <c r="C44" s="1">
         <v>25813</v>
       </c>
       <c r="D44" s="1">
-        <v>46435</v>
+        <v>36792</v>
       </c>
       <c r="E44" s="1">
-        <v>50004</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>33336</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>94129</v>
+        <v>80340</v>
       </c>
       <c r="C45" s="1">
         <v>25813</v>
       </c>
       <c r="D45" s="1">
+        <v>40925</v>
+      </c>
+      <c r="E45" s="1">
+        <v>40482</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="1">
+        <v>87942</v>
+      </c>
+      <c r="C46" s="1">
+        <v>25813</v>
+      </c>
+      <c r="D46" s="1">
+        <v>43680</v>
+      </c>
+      <c r="E46" s="1">
+        <v>45246</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="1">
+        <v>90649</v>
+      </c>
+      <c r="C47" s="1">
+        <v>25813</v>
+      </c>
+      <c r="D47" s="1">
+        <v>46435</v>
+      </c>
+      <c r="E47" s="1">
+        <v>50004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="1">
+        <v>94129</v>
+      </c>
+      <c r="C48" s="1">
+        <v>25813</v>
+      </c>
+      <c r="D48" s="1">
         <v>49190</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E48" s="1">
         <v>54774</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B49" s="1">
         <v>86650</v>
-      </c>
-      <c r="C46" s="1">
-        <v>34418</v>
-      </c>
-      <c r="D46" s="1">
-        <v>38080</v>
-      </c>
-      <c r="E46" s="1">
-        <v>29088</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="1">
-        <v>92782</v>
-      </c>
-      <c r="C47" s="1">
-        <v>34418</v>
-      </c>
-      <c r="D47" s="1">
-        <v>41395</v>
-      </c>
-      <c r="E47" s="1">
-        <v>35550</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="1">
-        <v>101660</v>
-      </c>
-      <c r="C48" s="1">
-        <v>34418</v>
-      </c>
-      <c r="D48" s="1">
-        <v>46368</v>
-      </c>
-      <c r="E48" s="1">
-        <v>47628</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" s="1">
-        <v>109037</v>
       </c>
       <c r="C49" s="1">
         <v>34418</v>
       </c>
       <c r="D49" s="1">
-        <v>51341</v>
+        <v>38080</v>
       </c>
       <c r="E49" s="1">
-        <v>57834</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>29088</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>116081</v>
+        <v>92782</v>
       </c>
       <c r="C50" s="1">
         <v>34418</v>
       </c>
       <c r="D50" s="1">
-        <v>54656</v>
+        <v>41395</v>
       </c>
       <c r="E50" s="1">
-        <v>64638</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>35550</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>123055</v>
+        <v>101660</v>
       </c>
       <c r="C51" s="1">
         <v>34418</v>
       </c>
       <c r="D51" s="1">
-        <v>57971</v>
+        <v>46368</v>
       </c>
       <c r="E51" s="1">
-        <v>71442</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47628</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>127846</v>
+        <v>109037</v>
       </c>
       <c r="C52" s="1">
         <v>34418</v>
       </c>
       <c r="D52" s="1">
+        <v>51341</v>
+      </c>
+      <c r="E52" s="1">
+        <v>57834</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="1">
+        <v>116081</v>
+      </c>
+      <c r="C53" s="1">
+        <v>34418</v>
+      </c>
+      <c r="D53" s="1">
+        <v>54656</v>
+      </c>
+      <c r="E53" s="1">
+        <v>64638</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="1">
+        <v>123055</v>
+      </c>
+      <c r="C54" s="1">
+        <v>34418</v>
+      </c>
+      <c r="D54" s="1">
+        <v>57971</v>
+      </c>
+      <c r="E54" s="1">
+        <v>71442</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="1">
+        <v>127846</v>
+      </c>
+      <c r="C55" s="1">
+        <v>34418</v>
+      </c>
+      <c r="D55" s="1">
         <v>61286</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E55" s="1">
         <v>78246</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B56" s="1">
         <v>134238</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C56" s="1">
         <v>36139</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D56" s="1">
         <v>64350</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E56" s="1">
         <v>82158</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE426D2-2546-4C09-9E49-393CA4A2B16B}">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>144222</v>
+      </c>
+      <c r="D2">
+        <v>15708</v>
+      </c>
+      <c r="E2">
+        <v>50203</v>
+      </c>
+      <c r="F2">
+        <v>61992</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>154959</v>
+      </c>
+      <c r="D3">
+        <v>18124</v>
+      </c>
+      <c r="E3">
+        <v>60570</v>
+      </c>
+      <c r="F3">
+        <v>69741</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>164244</v>
+      </c>
+      <c r="D4">
+        <v>22209</v>
+      </c>
+      <c r="E4">
+        <v>74200</v>
+      </c>
+      <c r="F4">
+        <v>77490</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>170596</v>
+      </c>
+      <c r="D5">
+        <v>24935</v>
+      </c>
+      <c r="E5">
+        <v>83282</v>
+      </c>
+      <c r="F5">
+        <v>82656</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>152076</v>
+      </c>
+      <c r="D6">
+        <v>16553</v>
+      </c>
+      <c r="E6">
+        <v>54955</v>
+      </c>
+      <c r="F6">
+        <v>67158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>158569</v>
+      </c>
+      <c r="D7">
+        <v>20183</v>
+      </c>
+      <c r="E7">
+        <v>67065</v>
+      </c>
+      <c r="F7">
+        <v>72324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>169835</v>
+      </c>
+      <c r="D8">
+        <v>24466</v>
+      </c>
+      <c r="E8">
+        <v>81769</v>
+      </c>
+      <c r="F8">
+        <v>80073</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>179119</v>
+      </c>
+      <c r="D9">
+        <v>29905</v>
+      </c>
+      <c r="E9">
+        <v>99909</v>
+      </c>
+      <c r="F9">
+        <v>87822</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>185471</v>
+      </c>
+      <c r="D10">
+        <v>33535</v>
+      </c>
+      <c r="E10">
+        <v>112026</v>
+      </c>
+      <c r="F10">
+        <v>92988</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>166951</v>
+      </c>
+      <c r="D11">
+        <v>20196</v>
+      </c>
+      <c r="E11">
+        <v>65886</v>
+      </c>
+      <c r="F11">
+        <v>77490</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>173444</v>
+      </c>
+      <c r="D12">
+        <v>24730</v>
+      </c>
+      <c r="E12">
+        <v>75676</v>
+      </c>
+      <c r="F12">
+        <v>82656</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13">
+        <v>184710</v>
+      </c>
+      <c r="D13">
+        <v>30809</v>
+      </c>
+      <c r="E13">
+        <v>89338</v>
+      </c>
+      <c r="F13">
+        <v>90405</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
+        <v>191175</v>
+      </c>
+      <c r="D14">
+        <v>37607</v>
+      </c>
+      <c r="E14">
+        <v>114160</v>
+      </c>
+      <c r="F14">
+        <v>98154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>200347</v>
+      </c>
+      <c r="D15">
+        <v>42141</v>
+      </c>
+      <c r="E15">
+        <v>125799</v>
+      </c>
+      <c r="F15">
+        <v>103320</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16">
+        <v>174777</v>
+      </c>
+      <c r="D16">
+        <v>22466</v>
+      </c>
+      <c r="E16">
+        <v>80013</v>
+      </c>
+      <c r="F16">
+        <v>82656</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>181270</v>
+      </c>
+      <c r="D17">
+        <v>26994</v>
+      </c>
+      <c r="E17">
+        <v>89362</v>
+      </c>
+      <c r="F17">
+        <v>87822</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18">
+        <v>192543</v>
+      </c>
+      <c r="D18">
+        <v>33073</v>
+      </c>
+      <c r="E18">
+        <v>103135</v>
+      </c>
+      <c r="F18">
+        <v>95571</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19">
+        <v>199000</v>
+      </c>
+      <c r="D19">
+        <v>39871</v>
+      </c>
+      <c r="E19">
+        <v>128280</v>
+      </c>
+      <c r="F19">
+        <v>103320</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20">
+        <v>208179</v>
+      </c>
+      <c r="D20">
+        <v>44405</v>
+      </c>
+      <c r="E20">
+        <v>139534</v>
+      </c>
+      <c r="F20">
+        <v>108486</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21">
+        <v>182398</v>
+      </c>
+      <c r="D21">
+        <v>24730</v>
+      </c>
+      <c r="E21">
+        <v>93854</v>
+      </c>
+      <c r="F21">
+        <v>87822</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <v>189123</v>
+      </c>
+      <c r="D22">
+        <v>29258</v>
+      </c>
+      <c r="E22">
+        <v>103458</v>
+      </c>
+      <c r="F22">
+        <v>92988</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23">
+        <v>201771</v>
+      </c>
+      <c r="D23">
+        <v>35277</v>
+      </c>
+      <c r="E23">
+        <v>117386</v>
+      </c>
+      <c r="F23">
+        <v>100737</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24">
+        <v>206798</v>
+      </c>
+      <c r="D24">
+        <v>42134</v>
+      </c>
+      <c r="E24">
+        <v>142072</v>
+      </c>
+      <c r="F24">
+        <v>108486</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25">
+        <v>216231</v>
+      </c>
+      <c r="D25">
+        <v>46669</v>
+      </c>
+      <c r="E25">
+        <v>153313</v>
+      </c>
+      <c r="F25">
+        <v>113652</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>212113</v>
+      </c>
+      <c r="D26">
+        <v>30756</v>
+      </c>
+      <c r="E26">
+        <v>110537</v>
+      </c>
+      <c r="F26">
+        <v>103320</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27">
+        <v>219248</v>
+      </c>
+      <c r="D27">
+        <v>37495</v>
+      </c>
+      <c r="E27">
+        <v>133256</v>
+      </c>
+      <c r="F27">
+        <v>108486</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28">
+        <v>231875</v>
+      </c>
+      <c r="D28">
+        <v>46669</v>
+      </c>
+      <c r="E28">
+        <v>167136</v>
+      </c>
+      <c r="F28">
+        <v>116235</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29">
+        <v>237381</v>
+      </c>
+      <c r="D29">
+        <v>56866</v>
+      </c>
+      <c r="E29">
+        <v>201202</v>
+      </c>
+      <c r="F29">
+        <v>123984</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30">
+        <v>245960</v>
+      </c>
+      <c r="D30">
+        <v>63670</v>
+      </c>
+      <c r="E30">
+        <v>223921</v>
+      </c>
+      <c r="F30">
+        <v>129150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31">
+        <v>260032</v>
+      </c>
+      <c r="D31">
+        <v>27199</v>
+      </c>
+      <c r="E31">
+        <v>96657</v>
+      </c>
+      <c r="F31">
+        <v>98154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>307140</v>
+      </c>
+      <c r="D32">
+        <v>45329</v>
+      </c>
+      <c r="E32">
+        <v>161093</v>
+      </c>
+      <c r="F32">
+        <v>129150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33">
+        <v>324913</v>
+      </c>
+      <c r="D33">
+        <v>49856</v>
+      </c>
+      <c r="E33">
+        <v>177203</v>
+      </c>
+      <c r="F33">
+        <v>136899</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEBDCEAF-E769-44C4-B34F-C931B2DDA697}">
+  <dimension ref="A1:B55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2">
+        <v>11094</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3">
+        <v>12830</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4">
+        <v>14565</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5">
+        <v>16300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6">
+        <v>18905</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7">
+        <v>21508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8">
+        <v>23244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9">
+        <v>17580</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>19772</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>21965</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>25254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>28542</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>30736</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15">
+        <v>32927</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16">
+        <v>35120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17">
+        <v>21508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18">
+        <v>23853</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19">
+        <v>27371</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20">
+        <v>30887</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21">
+        <v>33232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22">
+        <v>35578</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>161</v>
+      </c>
+      <c r="B23">
+        <v>37923</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24">
+        <v>24980</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>27630</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <v>31603</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27">
+        <v>35578</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28">
+        <v>38227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29">
+        <v>40877</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30">
+        <v>43526</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31">
+        <v>31405</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32">
+        <v>35836</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33">
+        <v>40268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34">
+        <v>43221</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36">
+        <v>49130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37">
+        <v>32982</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38">
+        <v>37565</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39">
+        <v>42148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40">
+        <v>45203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41">
+        <v>48257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42">
+        <v>51313</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43">
+        <v>38292</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>183</v>
+      </c>
+      <c r="B44">
+        <v>43518</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>184</v>
+      </c>
+      <c r="B45">
+        <v>48743</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>185</v>
+      </c>
+      <c r="B46">
+        <v>52226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>186</v>
+      </c>
+      <c r="B47">
+        <v>55709</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48">
+        <v>59193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49">
+        <v>41832</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50">
+        <v>47486</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51">
+        <v>53139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52">
+        <v>56908</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53">
+        <v>60677</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54">
+        <v>64446</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55">
+        <v>74000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A9F9EE-BDDB-4579-BA1F-FD3339C134CA}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2">
+        <v>62100</v>
+      </c>
+      <c r="E2">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3">
+        <v>62100</v>
+      </c>
+      <c r="E3">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4">
+        <v>66000</v>
+      </c>
+      <c r="E4">
+        <v>70100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5">
+        <v>112717</v>
+      </c>
+      <c r="E5">
+        <v>117180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6">
+        <v>112717</v>
+      </c>
+      <c r="E6">
+        <v>117180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7">
+        <v>116550</v>
+      </c>
+      <c r="E7">
+        <v>122300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8">
+        <v>184297</v>
+      </c>
+      <c r="E8">
+        <v>204498</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9">
+        <v>184297</v>
+      </c>
+      <c r="E9">
+        <v>204498</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10">
+        <v>194121</v>
+      </c>
+      <c r="E10">
+        <v>208575</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11">
+        <v>64350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F12">
+        <v>64350</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" t="s">
+        <v>195</v>
+      </c>
+      <c r="F13">
+        <v>67260</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14">
+        <v>133075</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" t="s">
+        <v>194</v>
+      </c>
+      <c r="F15">
+        <v>133875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16">
+        <v>145763</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17">
+        <v>174350</v>
+      </c>
+      <c r="E17">
+        <v>174350</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18">
+        <v>174350</v>
+      </c>
+      <c r="E18">
+        <v>174350</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19">
+        <v>186300</v>
+      </c>
+      <c r="E19">
+        <v>186300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D20">
+        <v>206731</v>
+      </c>
+      <c r="E20">
+        <v>206731</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21">
+        <v>206731</v>
+      </c>
+      <c r="E21">
+        <v>206731</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22">
+        <v>208285</v>
+      </c>
+      <c r="E22">
+        <v>208285</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C23" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23">
+        <v>271005</v>
+      </c>
+      <c r="E23">
+        <v>271005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24">
+        <v>271005</v>
+      </c>
+      <c r="E24">
+        <v>271005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25">
+        <v>286182</v>
+      </c>
+      <c r="E25">
+        <v>286182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A83AEA-1664-4235-A07C-8B238DD223C4}">
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8">
+        <v>10685</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9">
+        <v>20505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12">
+        <v>13517</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13">
+        <v>20505</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15">
+        <v>48364</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>218</v>
+      </c>
+      <c r="B17" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" t="s">
+        <v>229</v>
+      </c>
+      <c r="D17">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" t="s">
+        <v>233</v>
+      </c>
+      <c r="D21">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" t="s">
+        <v>234</v>
+      </c>
+      <c r="D22">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>230</v>
+      </c>
+      <c r="B23" t="s">
+        <v>235</v>
+      </c>
+      <c r="D23">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D24">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>230</v>
+      </c>
+      <c r="B25" t="s">
+        <v>237</v>
+      </c>
+      <c r="D25">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>238</v>
+      </c>
+      <c r="B27" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>241</v>
+      </c>
+      <c r="B29" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" t="s">
+        <v>243</v>
+      </c>
+      <c r="D30">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>241</v>
+      </c>
+      <c r="B31" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B32" t="s">
+        <v>245</v>
+      </c>
+      <c r="D32">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>241</v>
+      </c>
+      <c r="B33" t="s">
+        <v>246</v>
+      </c>
+      <c r="C33" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>241</v>
+      </c>
+      <c r="B34" t="s">
+        <v>246</v>
+      </c>
+      <c r="C34" t="s">
+        <v>221</v>
+      </c>
+      <c r="D34">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>241</v>
+      </c>
+      <c r="B36" t="s">
+        <v>248</v>
+      </c>
+      <c r="C36" t="s">
+        <v>220</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>241</v>
+      </c>
+      <c r="B37" t="s">
+        <v>248</v>
+      </c>
+      <c r="C37" t="s">
+        <v>221</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>249</v>
+      </c>
+      <c r="B38">
+        <v>80</v>
+      </c>
+      <c r="D38">
+        <v>101970</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>249</v>
+      </c>
+      <c r="B39">
+        <v>90</v>
+      </c>
+      <c r="D39">
+        <v>112167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40">
+        <v>16459</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41">
+        <v>21250</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42">
+        <v>27169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43">
+        <v>33410</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44">
+        <v>27012</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45">
+        <v>60797</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46">
+        <v>65546</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>251</v>
+      </c>
+      <c r="D47">
+        <v>73221</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>252</v>
+      </c>
+      <c r="D48">
+        <v>88575</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49">
+        <v>12600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82512D28-CBA6-44C4-BB91-2A44CD2A0064}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -1699,14 +4241,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1735,7 +4277,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1764,7 +4306,7 @@
         <v>36118</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1793,7 +4335,7 @@
         <v>41278</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1822,7 +4364,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1851,7 +4393,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1880,7 +4422,7 @@
         <v>59337</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1909,7 +4451,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1938,7 +4480,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1967,7 +4509,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1996,7 +4538,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -2025,7 +4567,7 @@
         <v>56757</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -2054,7 +4596,7 @@
         <v>61916</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -2083,7 +4625,7 @@
         <v>69656</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -2112,7 +4654,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -2141,7 +4683,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -2170,7 +4712,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -2199,7 +4741,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -2228,7 +4770,7 @@
         <v>79975</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -2257,7 +4799,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -2286,7 +4828,7 @@
         <v>92875</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,7 +4857,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -2344,7 +4886,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2373,7 +4915,7 @@
         <v>90295</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -2402,7 +4944,7 @@
         <v>98034</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -2431,7 +4973,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -2460,7 +5002,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -2489,7 +5031,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -2518,7 +5060,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,7 +5089,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -2576,7 +5118,7 @@
         <v>95454</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -2605,655 +5147,714 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="1">
+        <v>197481</v>
+      </c>
+      <c r="C32" s="1">
+        <v>18929</v>
+      </c>
+      <c r="D32" s="1">
+        <v>41525</v>
+      </c>
+      <c r="E32" s="1">
+        <v>35718</v>
+      </c>
+      <c r="F32" s="1">
+        <v>43266</v>
+      </c>
+      <c r="G32" s="1">
+        <v>56976</v>
+      </c>
+      <c r="H32" s="1">
+        <v>178371</v>
+      </c>
+      <c r="I32" s="1">
+        <v>113513</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="1">
+        <v>212169</v>
+      </c>
+      <c r="C33" s="1">
+        <v>18929</v>
+      </c>
+      <c r="D33" s="1">
+        <v>44100</v>
+      </c>
+      <c r="E33" s="1">
+        <v>39120</v>
+      </c>
+      <c r="F33" s="1">
+        <v>47388</v>
+      </c>
+      <c r="G33" s="1">
+        <v>62406</v>
+      </c>
+      <c r="H33" s="1">
+        <v>195360</v>
+      </c>
+      <c r="I33" s="1">
+        <v>118673</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B34" s="1">
         <v>135138</v>
-      </c>
-      <c r="C32" s="1">
-        <v>20650</v>
-      </c>
-      <c r="D32" s="1">
-        <v>27900</v>
-      </c>
-      <c r="E32" s="1">
-        <v>16842</v>
-      </c>
-      <c r="F32" s="1">
-        <v>20400</v>
-      </c>
-      <c r="G32" s="1">
-        <v>26862</v>
-      </c>
-      <c r="H32" s="1">
-        <v>84091</v>
-      </c>
-      <c r="I32" s="1">
-        <v>87715</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="1">
-        <v>143875</v>
-      </c>
-      <c r="C33" s="1">
-        <v>20650</v>
-      </c>
-      <c r="D33" s="1">
-        <v>30600</v>
-      </c>
-      <c r="E33" s="1">
-        <v>20580</v>
-      </c>
-      <c r="F33" s="1">
-        <v>24930</v>
-      </c>
-      <c r="G33" s="1">
-        <v>29844</v>
-      </c>
-      <c r="H33" s="1">
-        <v>102778</v>
-      </c>
-      <c r="I33" s="1">
-        <v>92875</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="1">
-        <v>159944</v>
       </c>
       <c r="C34" s="1">
         <v>20650</v>
       </c>
       <c r="D34" s="1">
-        <v>34650</v>
+        <v>27900</v>
       </c>
       <c r="E34" s="1">
-        <v>26196</v>
+        <v>16842</v>
       </c>
       <c r="F34" s="1">
-        <v>31728</v>
+        <v>20400</v>
       </c>
       <c r="G34" s="1">
-        <v>41784</v>
+        <v>26862</v>
       </c>
       <c r="H34" s="1">
-        <v>130806</v>
+        <v>84091</v>
       </c>
       <c r="I34" s="1">
-        <v>100614</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+        <v>87715</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B35" s="1">
-        <v>173644</v>
+        <v>143875</v>
       </c>
       <c r="C35" s="1">
         <v>20650</v>
       </c>
       <c r="D35" s="1">
-        <v>38700</v>
+        <v>30600</v>
       </c>
       <c r="E35" s="1">
-        <v>31806</v>
+        <v>20580</v>
       </c>
       <c r="F35" s="1">
-        <v>38532</v>
+        <v>24930</v>
       </c>
       <c r="G35" s="1">
-        <v>50736</v>
+        <v>29844</v>
       </c>
       <c r="H35" s="1">
-        <v>158834</v>
+        <v>102778</v>
       </c>
       <c r="I35" s="1">
-        <v>108354</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" s="1">
-        <v>189481</v>
+        <v>159944</v>
       </c>
       <c r="C36" s="1">
         <v>20650</v>
       </c>
       <c r="D36" s="1">
-        <v>41400</v>
+        <v>34650</v>
       </c>
       <c r="E36" s="1">
-        <v>35550</v>
+        <v>26196</v>
       </c>
       <c r="F36" s="1">
-        <v>43062</v>
+        <v>31728</v>
       </c>
       <c r="G36" s="1">
-        <v>56706</v>
+        <v>41784</v>
       </c>
       <c r="H36" s="1">
-        <v>177522</v>
+        <v>130806</v>
       </c>
       <c r="I36" s="1">
-        <v>113513</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+        <v>100614</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37" s="1">
-        <v>205731</v>
+        <v>173644</v>
       </c>
       <c r="C37" s="1">
         <v>20650</v>
       </c>
       <c r="D37" s="1">
-        <v>44100</v>
+        <v>38700</v>
       </c>
       <c r="E37" s="1">
-        <v>39294</v>
+        <v>31806</v>
       </c>
       <c r="F37" s="1">
-        <v>47598</v>
+        <v>38532</v>
       </c>
       <c r="G37" s="1">
-        <v>62676</v>
+        <v>50736</v>
       </c>
       <c r="H37" s="1">
-        <v>196209</v>
+        <v>158834</v>
       </c>
       <c r="I37" s="1">
-        <v>118673</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <v>108354</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1">
-        <v>218806</v>
+        <v>189481</v>
       </c>
       <c r="C38" s="1">
         <v>20650</v>
       </c>
       <c r="D38" s="1">
+        <v>41400</v>
+      </c>
+      <c r="E38" s="1">
+        <v>35550</v>
+      </c>
+      <c r="F38" s="1">
+        <v>43062</v>
+      </c>
+      <c r="G38" s="1">
+        <v>56706</v>
+      </c>
+      <c r="H38" s="1">
+        <v>177522</v>
+      </c>
+      <c r="I38" s="1">
+        <v>113513</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="1">
+        <v>205731</v>
+      </c>
+      <c r="C39" s="1">
+        <v>20650</v>
+      </c>
+      <c r="D39" s="1">
+        <v>44100</v>
+      </c>
+      <c r="E39" s="1">
+        <v>39294</v>
+      </c>
+      <c r="F39" s="1">
+        <v>47598</v>
+      </c>
+      <c r="G39" s="1">
+        <v>62676</v>
+      </c>
+      <c r="H39" s="1">
+        <v>196209</v>
+      </c>
+      <c r="I39" s="1">
+        <v>118673</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="1">
+        <v>218806</v>
+      </c>
+      <c r="C40" s="1">
+        <v>20650</v>
+      </c>
+      <c r="D40" s="1">
         <v>46800</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E40" s="1">
         <v>43038</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F40" s="1">
         <v>52128</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G40" s="1">
         <v>68646</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H40" s="1">
         <v>214897</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I40" s="1">
         <v>123833</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B41" s="1">
         <v>145750</v>
-      </c>
-      <c r="C39" s="1">
-        <v>25813</v>
-      </c>
-      <c r="D39" s="1">
-        <v>33375</v>
-      </c>
-      <c r="E39" s="1">
-        <v>21432</v>
-      </c>
-      <c r="F39" s="1">
-        <v>25962</v>
-      </c>
-      <c r="G39" s="1">
-        <v>34188</v>
-      </c>
-      <c r="H39" s="1">
-        <v>107024</v>
-      </c>
-      <c r="I39" s="1">
-        <v>103194</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="1">
-        <v>154494</v>
-      </c>
-      <c r="C40" s="1">
-        <v>25813</v>
-      </c>
-      <c r="D40" s="1">
-        <v>36450</v>
-      </c>
-      <c r="E40" s="1">
-        <v>26196</v>
-      </c>
-      <c r="F40" s="1">
-        <v>31728</v>
-      </c>
-      <c r="G40" s="1">
-        <v>41784</v>
-      </c>
-      <c r="H40" s="1">
-        <v>130806</v>
-      </c>
-      <c r="I40" s="1">
-        <v>108354</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="1">
-        <v>171738</v>
       </c>
       <c r="C41" s="1">
         <v>25813</v>
       </c>
       <c r="D41" s="1">
-        <v>41063</v>
+        <v>33375</v>
       </c>
       <c r="E41" s="1">
-        <v>33336</v>
+        <v>21432</v>
       </c>
       <c r="F41" s="1">
-        <v>40386</v>
+        <v>25962</v>
       </c>
       <c r="G41" s="1">
-        <v>53178</v>
+        <v>34188</v>
       </c>
       <c r="H41" s="1">
-        <v>166483</v>
+        <v>107024</v>
       </c>
       <c r="I41" s="1">
-        <v>116093</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+        <v>103194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B42" s="1">
-        <v>184256</v>
+        <v>154494</v>
       </c>
       <c r="C42" s="1">
         <v>25813</v>
       </c>
       <c r="D42" s="1">
-        <v>45675</v>
+        <v>36450</v>
       </c>
       <c r="E42" s="1">
-        <v>40482</v>
+        <v>26196</v>
       </c>
       <c r="F42" s="1">
-        <v>49032</v>
+        <v>31728</v>
       </c>
       <c r="G42" s="1">
-        <v>64572</v>
+        <v>41784</v>
       </c>
       <c r="H42" s="1">
-        <v>202153</v>
+        <v>130806</v>
       </c>
       <c r="I42" s="1">
-        <v>123833</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>108354</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B43" s="1">
-        <v>200094</v>
+        <v>171738</v>
       </c>
       <c r="C43" s="1">
         <v>25813</v>
       </c>
       <c r="D43" s="1">
-        <v>48750</v>
+        <v>41063</v>
       </c>
       <c r="E43" s="1">
-        <v>45246</v>
+        <v>33336</v>
       </c>
       <c r="F43" s="1">
-        <v>54804</v>
+        <v>40386</v>
       </c>
       <c r="G43" s="1">
-        <v>72174</v>
+        <v>53178</v>
       </c>
       <c r="H43" s="1">
-        <v>225949</v>
+        <v>166483</v>
       </c>
       <c r="I43" s="1">
-        <v>128993</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>116093</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B44" s="1">
-        <v>217975</v>
+        <v>184256</v>
       </c>
       <c r="C44" s="1">
         <v>25813</v>
       </c>
       <c r="D44" s="1">
-        <v>51825</v>
+        <v>45675</v>
       </c>
       <c r="E44" s="1">
-        <v>50004</v>
+        <v>40482</v>
       </c>
       <c r="F44" s="1">
-        <v>60576</v>
+        <v>49032</v>
       </c>
       <c r="G44" s="1">
-        <v>79770</v>
+        <v>64572</v>
       </c>
       <c r="H44" s="1">
-        <v>249718</v>
+        <v>202153</v>
       </c>
       <c r="I44" s="1">
-        <v>134152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+        <v>123833</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B45" s="1">
-        <v>229094</v>
+        <v>200094</v>
       </c>
       <c r="C45" s="1">
         <v>25813</v>
       </c>
       <c r="D45" s="1">
+        <v>48750</v>
+      </c>
+      <c r="E45" s="1">
+        <v>45246</v>
+      </c>
+      <c r="F45" s="1">
+        <v>48804</v>
+      </c>
+      <c r="G45" s="1">
+        <v>72174</v>
+      </c>
+      <c r="H45" s="1">
+        <v>225949</v>
+      </c>
+      <c r="I45" s="1">
+        <v>128993</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="1">
+        <v>217975</v>
+      </c>
+      <c r="C46" s="1">
+        <v>25813</v>
+      </c>
+      <c r="D46" s="1">
+        <v>51825</v>
+      </c>
+      <c r="E46" s="1">
+        <v>50004</v>
+      </c>
+      <c r="F46" s="1">
+        <v>60576</v>
+      </c>
+      <c r="G46" s="1">
+        <v>79770</v>
+      </c>
+      <c r="H46" s="1">
+        <v>249718</v>
+      </c>
+      <c r="I46" s="1">
+        <v>134152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="1">
+        <v>229094</v>
+      </c>
+      <c r="C47" s="1">
+        <v>25813</v>
+      </c>
+      <c r="D47" s="1">
         <v>54900</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E47" s="1">
         <v>54774</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F47" s="1">
         <v>66342</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G47" s="1">
         <v>87366</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H47" s="1">
         <v>273507</v>
       </c>
-      <c r="I45" s="1">
+      <c r="I47" s="1">
         <v>139312</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B48" s="1">
         <v>193250</v>
-      </c>
-      <c r="C46" s="1">
-        <v>34418</v>
-      </c>
-      <c r="D46" s="1">
-        <v>42500</v>
-      </c>
-      <c r="E46" s="1">
-        <v>29088</v>
-      </c>
-      <c r="F46" s="1">
-        <v>35232</v>
-      </c>
-      <c r="G46" s="1">
-        <v>46398</v>
-      </c>
-      <c r="H46" s="1">
-        <v>145241</v>
-      </c>
-      <c r="I46" s="1">
-        <v>128993</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="1">
-        <v>208394</v>
-      </c>
-      <c r="C47" s="1">
-        <v>34418</v>
-      </c>
-      <c r="D47" s="1">
-        <v>46200</v>
-      </c>
-      <c r="E47" s="1">
-        <v>35550</v>
-      </c>
-      <c r="F47" s="1">
-        <v>43062</v>
-      </c>
-      <c r="G47" s="1">
-        <v>56706</v>
-      </c>
-      <c r="H47" s="1">
-        <v>177522</v>
-      </c>
-      <c r="I47" s="1">
-        <v>134152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="1">
-        <v>225888</v>
       </c>
       <c r="C48" s="1">
         <v>34418</v>
       </c>
       <c r="D48" s="1">
-        <v>51750</v>
+        <v>42500</v>
       </c>
       <c r="E48" s="1">
-        <v>47628</v>
+        <v>29088</v>
       </c>
       <c r="F48" s="1">
-        <v>54804</v>
+        <v>35232</v>
       </c>
       <c r="G48" s="1">
-        <v>72174</v>
+        <v>46398</v>
       </c>
       <c r="H48" s="1">
-        <v>225942</v>
+        <v>145241</v>
       </c>
       <c r="I48" s="1">
-        <v>141892</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+        <v>128993</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B49" s="1">
-        <v>240975</v>
+        <v>208394</v>
       </c>
       <c r="C49" s="1">
         <v>34418</v>
       </c>
       <c r="D49" s="1">
-        <v>57300</v>
+        <v>46200</v>
       </c>
       <c r="E49" s="1">
-        <v>57834</v>
+        <v>35550</v>
       </c>
       <c r="F49" s="1">
-        <v>66552</v>
+        <v>43062</v>
       </c>
       <c r="G49" s="1">
-        <v>87636</v>
+        <v>56706</v>
       </c>
       <c r="H49" s="1">
-        <v>274356</v>
+        <v>177522</v>
       </c>
       <c r="I49" s="1">
-        <v>149631</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+        <v>134152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B50" s="1">
-        <v>261844</v>
+        <v>225888</v>
       </c>
       <c r="C50" s="1">
         <v>34418</v>
       </c>
       <c r="D50" s="1">
-        <v>61000</v>
+        <v>51750</v>
       </c>
       <c r="E50" s="1">
-        <v>64638</v>
+        <v>47628</v>
       </c>
       <c r="F50" s="1">
-        <v>74382</v>
+        <v>54804</v>
       </c>
       <c r="G50" s="1">
-        <v>97950</v>
+        <v>72174</v>
       </c>
       <c r="H50" s="1">
-        <v>306630</v>
+        <v>225942</v>
       </c>
       <c r="I50" s="1">
-        <v>154791</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+        <v>141892</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B51" s="1">
-        <v>275019</v>
+        <v>240975</v>
       </c>
       <c r="C51" s="1">
         <v>34418</v>
       </c>
       <c r="D51" s="1">
-        <v>64700</v>
+        <v>57300</v>
       </c>
       <c r="E51" s="1">
-        <v>71442</v>
+        <v>57834</v>
       </c>
       <c r="F51" s="1">
-        <v>82212</v>
+        <v>66552</v>
       </c>
       <c r="G51" s="1">
-        <v>108258</v>
+        <v>87636</v>
       </c>
       <c r="H51" s="1">
-        <v>338903</v>
+        <v>274356</v>
       </c>
       <c r="I51" s="1">
-        <v>159951</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+        <v>149631</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B52" s="1">
-        <v>292225</v>
+        <v>261844</v>
       </c>
       <c r="C52" s="1">
         <v>34418</v>
       </c>
       <c r="D52" s="1">
+        <v>61000</v>
+      </c>
+      <c r="E52" s="1">
+        <v>64638</v>
+      </c>
+      <c r="F52" s="1">
+        <v>74382</v>
+      </c>
+      <c r="G52" s="1">
+        <v>97950</v>
+      </c>
+      <c r="H52" s="1">
+        <v>306630</v>
+      </c>
+      <c r="I52" s="1">
+        <v>154791</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="1">
+        <v>275019</v>
+      </c>
+      <c r="C53" s="1">
+        <v>34418</v>
+      </c>
+      <c r="D53" s="1">
+        <v>64700</v>
+      </c>
+      <c r="E53" s="1">
+        <v>71442</v>
+      </c>
+      <c r="F53" s="1">
+        <v>82212</v>
+      </c>
+      <c r="G53" s="1">
+        <v>108258</v>
+      </c>
+      <c r="H53" s="1">
+        <v>338903</v>
+      </c>
+      <c r="I53" s="1">
+        <v>159951</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="1">
+        <v>292225</v>
+      </c>
+      <c r="C54" s="1">
+        <v>34418</v>
+      </c>
+      <c r="D54" s="1">
         <v>68400</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E54" s="1">
         <v>78246</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F54" s="1">
         <v>90042</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G54" s="1">
         <v>118566</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H54" s="1">
         <v>371184</v>
       </c>
-      <c r="I52" s="1">
+      <c r="I54" s="1">
         <v>165110</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B55" s="1">
         <v>306836</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C55" s="1">
         <v>36139</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D55" s="1">
         <v>71820</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E55" s="1">
         <v>82158</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F55" s="1">
         <v>94544</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G55" s="1">
         <v>124494</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H55" s="1">
         <v>389743</v>
       </c>
-      <c r="I53" s="1">
+      <c r="I55" s="1">
         <v>173366</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3279,7 +5880,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -3305,7 +5906,7 @@
         <v>12649</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -3331,7 +5932,7 @@
         <v>16877</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3357,7 +5958,7 @@
         <v>21105</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -3383,7 +5984,7 @@
         <v>25332</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -3409,7 +6010,7 @@
         <v>29560</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -3435,7 +6036,7 @@
         <v>33788</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3461,7 +6062,7 @@
         <v>38016</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -3487,7 +6088,7 @@
         <v>16877</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -3513,7 +6114,7 @@
         <v>22499</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -3539,7 +6140,7 @@
         <v>28120</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -3565,7 +6166,7 @@
         <v>33742</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -3591,7 +6192,7 @@
         <v>39364</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -3617,7 +6218,7 @@
         <v>44986</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -3643,7 +6244,7 @@
         <v>50607</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -3669,7 +6270,7 @@
         <v>21105</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -3695,7 +6296,7 @@
         <v>28120</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -3721,7 +6322,7 @@
         <v>35136</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -3747,7 +6348,7 @@
         <v>42152</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -3773,7 +6374,7 @@
         <v>49167</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -3799,7 +6400,7 @@
         <v>56183</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -3825,7 +6426,7 @@
         <v>63199</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -3851,7 +6452,7 @@
         <v>25332</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -3877,7 +6478,7 @@
         <v>33742</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -3903,7 +6504,7 @@
         <v>42152</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -3929,7 +6530,7 @@
         <v>50561</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -3955,7 +6556,7 @@
         <v>58971</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -3981,7 +6582,7 @@
         <v>67380</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -4007,7 +6608,7 @@
         <v>75790</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4033,7 +6634,7 @@
         <v>29560</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -4059,7 +6660,7 @@
         <v>39364</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -4085,7 +6686,7 @@
         <v>58971</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -4111,7 +6712,7 @@
         <v>68774</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -4137,7 +6738,7 @@
         <v>78578</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -4163,7 +6764,7 @@
         <v>88381</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -4189,7 +6790,7 @@
         <v>33788</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -4215,7 +6816,7 @@
         <v>44986</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -4241,7 +6842,7 @@
         <v>56183</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -4267,7 +6868,7 @@
         <v>67380</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -4293,7 +6894,7 @@
         <v>78578</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -4319,7 +6920,7 @@
         <v>89775</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -4345,7 +6946,7 @@
         <v>100973</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -4371,7 +6972,7 @@
         <v>38016</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -4397,7 +6998,7 @@
         <v>50607</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -4423,7 +7024,7 @@
         <v>63199</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -4449,7 +7050,7 @@
         <v>75790</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -4475,7 +7076,7 @@
         <v>88381</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -4501,7 +7102,7 @@
         <v>100973</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -4527,7 +7128,7 @@
         <v>113564</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -4553,7 +7154,7 @@
         <v>42175</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -4579,7 +7180,7 @@
         <v>56241</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -4605,7 +7206,7 @@
         <v>70307</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -4631,7 +7232,7 @@
         <v>84372</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -4657,7 +7258,7 @@
         <v>98438</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -4683,7 +7284,7 @@
         <v>112504</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -4709,7 +7310,7 @@
         <v>126570</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -4735,7 +7336,7 @@
         <v>46391</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -4761,7 +7362,7 @@
         <v>61862</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -4787,7 +7388,7 @@
         <v>77334</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -4813,7 +7414,7 @@
         <v>92805</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -4839,7 +7440,7 @@
         <v>108276</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -4865,7 +7466,7 @@
         <v>123748</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>35</v>
       </c>
@@ -4891,7 +7492,7 @@
         <v>139219</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -4917,7 +7518,7 @@
         <v>59052</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -4943,7 +7544,7 @@
         <v>78728</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -4969,7 +7570,7 @@
         <v>98404</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -4995,7 +7596,7 @@
         <v>118080</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -5021,7 +7622,7 @@
         <v>130499</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -5047,7 +7648,7 @@
         <v>142917</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -5079,11 +7680,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5112,7 +7713,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -5141,7 +7742,7 @@
         <v>24806</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -5170,7 +7771,7 @@
         <v>27907</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -5199,7 +7800,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -5228,7 +7829,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -5257,7 +7858,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -5286,7 +7887,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5315,7 +7916,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -5344,7 +7945,7 @@
         <v>27907</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -5373,7 +7974,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -5402,7 +8003,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -5431,7 +8032,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -5460,7 +8061,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -5489,7 +8090,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -5518,7 +8119,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -5547,7 +8148,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -5576,7 +8177,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -5605,7 +8206,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -5634,7 +8235,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -5663,7 +8264,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -5692,7 +8293,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -5721,7 +8322,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -5750,7 +8351,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -5779,7 +8380,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -5808,7 +8409,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -5837,7 +8438,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -5866,7 +8467,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -5895,7 +8496,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -5924,7 +8525,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -5953,7 +8554,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -5982,7 +8583,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -6011,7 +8612,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -6040,7 +8641,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -6069,7 +8670,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -6098,7 +8699,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -6127,7 +8728,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -6156,7 +8757,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -6185,7 +8786,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -6214,7 +8815,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -6243,7 +8844,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -6272,7 +8873,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -6301,7 +8902,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -6330,7 +8931,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -6359,7 +8960,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -6388,7 +8989,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -6417,7 +9018,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -6446,7 +9047,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -6475,7 +9076,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -6504,7 +9105,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -6533,7 +9134,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -6562,7 +9163,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -6591,7 +9192,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -6620,7 +9221,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -6649,7 +9250,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -6678,7 +9279,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -6707,7 +9308,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -6736,7 +9337,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -6765,7 +9366,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -6794,7 +9395,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -6823,7 +9424,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -6852,7 +9453,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -6881,7 +9482,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>35</v>
       </c>
@@ -6910,7 +9511,7 @@
         <v>68218</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -6939,7 +9540,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -6968,7 +9569,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -6997,7 +9598,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -7026,7 +9627,7 @@
         <v>68218</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -7055,7 +9656,7 @@
         <v>71318</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -7084,7 +9685,7 @@
         <v>74419</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -7119,11 +9720,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -7148,193 +9749,1335 @@
       <c r="H1" t="s">
         <v>60</v>
       </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2">
+        <v>122701</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>25448</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>28009</v>
+      </c>
+      <c r="G2">
+        <v>72521</v>
+      </c>
+      <c r="H2">
+        <v>108521</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3">
+        <v>162622</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>25448</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>28009</v>
+      </c>
+      <c r="G3">
+        <v>72521</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4">
+        <v>129329</v>
+      </c>
+      <c r="C4">
+        <v>19890</v>
+      </c>
+      <c r="D4">
+        <v>24115</v>
+      </c>
+      <c r="E4">
+        <v>31746</v>
+      </c>
+      <c r="F4">
+        <v>26533</v>
+      </c>
+      <c r="G4">
+        <v>68705</v>
+      </c>
+      <c r="H4">
+        <v>83034</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5">
+        <v>171098</v>
+      </c>
+      <c r="C5">
+        <v>9945</v>
+      </c>
+      <c r="D5">
+        <v>12058</v>
+      </c>
+      <c r="E5">
+        <v>15873</v>
+      </c>
+      <c r="F5">
+        <v>13267</v>
+      </c>
+      <c r="G5">
+        <v>34353</v>
+      </c>
+      <c r="H5">
+        <v>41517</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6">
+        <v>195833</v>
+      </c>
+      <c r="C6">
+        <v>9945</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>13267</v>
+      </c>
+      <c r="G6">
+        <v>34353</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7">
+        <v>191983</v>
+      </c>
+      <c r="C7">
+        <v>5558</v>
+      </c>
+      <c r="D7">
+        <v>6695</v>
+      </c>
+      <c r="E7">
+        <v>8821</v>
+      </c>
+      <c r="F7">
+        <v>7371</v>
+      </c>
+      <c r="G7">
+        <v>19084</v>
+      </c>
+      <c r="H7">
+        <v>23064</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8">
+        <v>208415</v>
+      </c>
+      <c r="C8">
+        <v>5558</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>7371</v>
+      </c>
+      <c r="G8">
+        <v>19084</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9">
+        <v>206271</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10">
+        <v>190883</v>
+      </c>
+      <c r="C10">
+        <v>9945</v>
+      </c>
+      <c r="D10">
+        <v>12058</v>
+      </c>
+      <c r="E10">
+        <v>15873</v>
+      </c>
+      <c r="F10">
+        <v>13267</v>
+      </c>
+      <c r="G10">
+        <v>34353</v>
+      </c>
+      <c r="H10">
+        <v>41517</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11">
+        <v>201875</v>
+      </c>
+      <c r="C11">
+        <v>5558</v>
+      </c>
+      <c r="D11">
+        <v>6695</v>
+      </c>
+      <c r="E11">
+        <v>8821</v>
+      </c>
+      <c r="F11">
+        <v>7371</v>
+      </c>
+      <c r="G11">
+        <v>19084</v>
+      </c>
+      <c r="H11">
+        <v>23064</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12">
+        <v>144718</v>
+      </c>
+      <c r="C12">
+        <v>22230</v>
+      </c>
+      <c r="D12">
+        <v>26780</v>
+      </c>
+      <c r="E12">
+        <v>35282</v>
+      </c>
+      <c r="F12">
+        <v>29484</v>
+      </c>
+      <c r="G12">
+        <v>76336</v>
+      </c>
+      <c r="H12">
+        <v>92257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13">
+        <v>195280</v>
+      </c>
+      <c r="C13">
+        <v>7001</v>
+      </c>
+      <c r="D13">
+        <v>8483</v>
+      </c>
+      <c r="E13">
+        <v>11174</v>
+      </c>
+      <c r="F13">
+        <v>9360</v>
+      </c>
+      <c r="G13">
+        <v>24180</v>
+      </c>
+      <c r="H13">
+        <v>29219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14">
+        <v>207370</v>
+      </c>
+      <c r="C14">
+        <v>3868</v>
+      </c>
+      <c r="D14">
+        <v>5356</v>
+      </c>
+      <c r="E14">
+        <v>7053</v>
+      </c>
+      <c r="F14">
+        <v>5896</v>
+      </c>
+      <c r="G14">
+        <v>15269</v>
+      </c>
+      <c r="H14">
+        <v>18446</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15">
+        <v>223579</v>
+      </c>
+      <c r="C15">
+        <v>3868</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>5896</v>
+      </c>
+      <c r="G15">
+        <v>15269</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16">
+        <v>180990</v>
+      </c>
+      <c r="C16">
+        <v>15477</v>
+      </c>
+      <c r="D16">
+        <v>20085</v>
+      </c>
+      <c r="E16">
+        <v>26455</v>
+      </c>
+      <c r="F16">
+        <v>22113</v>
+      </c>
+      <c r="G16">
+        <v>57259</v>
+      </c>
+      <c r="H16">
+        <v>69199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17">
+        <v>150213</v>
+      </c>
+      <c r="C17">
+        <v>15477</v>
+      </c>
+      <c r="D17">
+        <v>20085</v>
+      </c>
+      <c r="E17">
+        <v>26455</v>
+      </c>
+      <c r="F17">
+        <v>22113</v>
+      </c>
+      <c r="G17">
+        <v>57259</v>
+      </c>
+      <c r="H17">
+        <v>69199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18">
+        <v>283039</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783F635A-904E-4A2A-ABB3-ADAB2016D027}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2">
+        <v>99635</v>
+      </c>
+      <c r="C2">
+        <v>16965</v>
+      </c>
+      <c r="D2">
+        <v>72556</v>
+      </c>
+      <c r="E2">
+        <v>18675</v>
+      </c>
+      <c r="F2">
+        <v>48354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3">
+        <v>114030</v>
+      </c>
+      <c r="C3">
+        <v>16965</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>18675</v>
+      </c>
+      <c r="F3">
+        <v>48354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4">
+        <v>123971</v>
+      </c>
+      <c r="C4">
+        <v>13390</v>
+      </c>
+      <c r="D4">
+        <v>57283</v>
+      </c>
+      <c r="E4">
+        <v>14742</v>
+      </c>
+      <c r="F4">
+        <v>38175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5">
+        <v>138474</v>
+      </c>
+      <c r="C5">
+        <v>13390</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>14742</v>
+      </c>
+      <c r="F5">
+        <v>38175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6">
+        <v>150387</v>
+      </c>
+      <c r="C6">
+        <v>8931</v>
+      </c>
+      <c r="D6">
+        <v>38189</v>
+      </c>
+      <c r="E6">
+        <v>9828</v>
+      </c>
+      <c r="F6">
+        <v>25448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7">
+        <v>158256</v>
+      </c>
+      <c r="C7">
+        <v>8931</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>9828</v>
+      </c>
+      <c r="F7">
+        <v>25448</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8">
+        <v>119776</v>
+      </c>
+      <c r="C8">
+        <v>22321</v>
+      </c>
+      <c r="D8">
+        <v>95472</v>
+      </c>
+      <c r="E8">
+        <v>24570</v>
+      </c>
+      <c r="F8">
+        <v>63622</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9">
+        <v>115000</v>
+      </c>
+      <c r="C9">
+        <v>19500</v>
+      </c>
+      <c r="D9">
+        <v>65000</v>
+      </c>
+      <c r="E9">
+        <v>19000</v>
+      </c>
+      <c r="F9">
+        <v>49000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE0A675-4F8B-4A13-BCE1-53842A29437E}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
       <c r="I1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>262845</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>25839</v>
+      </c>
+      <c r="E2">
+        <v>34030</v>
+      </c>
+      <c r="F2">
+        <v>28439</v>
+      </c>
+      <c r="G2">
+        <v>73636</v>
+      </c>
+      <c r="H2">
+        <v>110191</v>
+      </c>
+      <c r="I2">
+        <v>70560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3">
+        <v>290723</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>25839</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>28439</v>
+      </c>
+      <c r="G3">
+        <v>73636</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4">
+        <v>272881</v>
+      </c>
+      <c r="C4">
+        <v>20196</v>
+      </c>
+      <c r="D4">
+        <v>24486</v>
+      </c>
+      <c r="E4">
+        <v>32234</v>
+      </c>
+      <c r="F4">
+        <v>26941</v>
+      </c>
+      <c r="G4">
+        <v>69762</v>
+      </c>
+      <c r="H4">
+        <v>104386</v>
+      </c>
+      <c r="I4">
+        <v>90720</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5">
+        <v>323060</v>
+      </c>
+      <c r="C5">
+        <v>10098</v>
+      </c>
+      <c r="D5">
+        <v>12243</v>
+      </c>
+      <c r="E5">
+        <v>16117</v>
+      </c>
+      <c r="F5">
+        <v>13471</v>
+      </c>
+      <c r="G5">
+        <v>34881</v>
+      </c>
+      <c r="H5">
+        <v>52193</v>
+      </c>
+      <c r="I5">
+        <v>45360</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6">
+        <v>338672</v>
+      </c>
+      <c r="C6">
+        <v>10098</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>13471</v>
+      </c>
+      <c r="G6">
+        <v>34881</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7">
+        <v>339787</v>
+      </c>
+      <c r="C7">
+        <v>5643</v>
+      </c>
+      <c r="D7">
+        <v>6798</v>
+      </c>
+      <c r="E7">
+        <v>8956</v>
+      </c>
+      <c r="F7">
+        <v>7484</v>
+      </c>
+      <c r="G7">
+        <v>19378</v>
+      </c>
+      <c r="H7">
+        <v>28995</v>
+      </c>
+      <c r="I7">
+        <v>32760</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8">
+        <v>348708</v>
+      </c>
+      <c r="C8">
+        <v>5643</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>7484</v>
+      </c>
+      <c r="G8">
+        <v>19378</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9">
+        <v>363204</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10">
+        <v>348708</v>
+      </c>
+      <c r="C10">
+        <v>10098</v>
+      </c>
+      <c r="D10">
+        <v>12243</v>
+      </c>
+      <c r="E10">
+        <v>16117</v>
+      </c>
+      <c r="F10">
+        <v>13471</v>
+      </c>
+      <c r="G10">
+        <v>34881</v>
+      </c>
+      <c r="H10">
+        <v>52193</v>
+      </c>
+      <c r="I10">
+        <v>95760</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11">
+        <v>349823</v>
+      </c>
+      <c r="C11">
+        <v>5643</v>
+      </c>
+      <c r="D11">
+        <v>6798</v>
+      </c>
+      <c r="E11">
+        <v>8956</v>
+      </c>
+      <c r="F11">
+        <v>7484</v>
+      </c>
+      <c r="G11">
+        <v>19378</v>
+      </c>
+      <c r="H11">
+        <v>28995</v>
+      </c>
+      <c r="I11">
+        <v>57960</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12">
+        <v>292953</v>
+      </c>
+      <c r="C12">
+        <v>22572</v>
+      </c>
+      <c r="D12">
+        <v>27192</v>
+      </c>
+      <c r="E12">
+        <v>35825</v>
+      </c>
+      <c r="F12">
+        <v>29938</v>
+      </c>
+      <c r="G12">
+        <v>77510</v>
+      </c>
+      <c r="H12">
+        <v>115980</v>
+      </c>
+      <c r="I12">
+        <v>131040</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13">
+        <v>357629</v>
+      </c>
+      <c r="C13">
+        <v>7108</v>
+      </c>
+      <c r="D13">
+        <v>8613</v>
+      </c>
+      <c r="E13">
+        <v>11345</v>
+      </c>
+      <c r="F13">
+        <v>9504</v>
+      </c>
+      <c r="G13">
+        <v>24552</v>
+      </c>
+      <c r="H13">
+        <v>36733</v>
+      </c>
+      <c r="I13">
+        <v>59220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14">
+        <v>365210</v>
+      </c>
+      <c r="C14">
+        <v>3927</v>
+      </c>
+      <c r="D14">
+        <v>5438</v>
+      </c>
+      <c r="E14">
+        <v>7161</v>
+      </c>
+      <c r="F14">
+        <v>5986</v>
+      </c>
+      <c r="G14">
+        <v>15503</v>
+      </c>
+      <c r="H14">
+        <v>23190</v>
+      </c>
+      <c r="I14">
+        <v>34020</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15">
+        <v>416021</v>
+      </c>
+      <c r="C15">
+        <v>3927</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>5986</v>
+      </c>
+      <c r="G15">
+        <v>15503</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16">
+        <v>335002</v>
+      </c>
+      <c r="C16">
+        <v>15715</v>
+      </c>
+      <c r="D16">
+        <v>20394</v>
+      </c>
+      <c r="E16">
+        <v>26862</v>
+      </c>
+      <c r="F16">
+        <v>22453</v>
+      </c>
+      <c r="G16">
+        <v>58139</v>
+      </c>
+      <c r="H16">
+        <v>86993</v>
+      </c>
+      <c r="I16">
+        <v>133560</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17">
+        <v>301874</v>
+      </c>
+      <c r="C17">
+        <v>15715</v>
+      </c>
+      <c r="D17">
+        <v>20394</v>
+      </c>
+      <c r="E17">
+        <v>26862</v>
+      </c>
+      <c r="F17">
+        <v>22453</v>
+      </c>
+      <c r="G17">
+        <v>58139</v>
+      </c>
+      <c r="H17">
+        <v>86993</v>
+      </c>
+      <c r="I17">
+        <v>57960</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18">
+        <v>391082</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD041F75-528C-4B17-92E2-D6C4283D27D6}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>126</v>
       </c>
       <c r="B2">
-        <v>122701</v>
+        <v>116380</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>25448</v>
+        <v>25839</v>
       </c>
       <c r="E2">
+        <v>28439</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3">
+        <v>105289</v>
+      </c>
+      <c r="C3">
+        <v>20196</v>
+      </c>
+      <c r="D3">
+        <v>24486</v>
+      </c>
+      <c r="E3">
+        <v>26941</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4">
+        <v>140475</v>
+      </c>
+      <c r="C4">
+        <v>10098</v>
+      </c>
+      <c r="D4">
+        <v>12243</v>
+      </c>
+      <c r="E4">
+        <v>13471</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5">
+        <v>168040</v>
+      </c>
+      <c r="C5">
+        <v>10098</v>
+      </c>
+      <c r="D5">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>28009</v>
-      </c>
-      <c r="G2">
-        <v>72521</v>
-      </c>
-      <c r="H2">
-        <v>108521</v>
-      </c>
-      <c r="I2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3">
-        <v>162622</v>
-      </c>
-      <c r="C3">
+      <c r="E5">
+        <v>13471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6">
+        <v>157887</v>
+      </c>
+      <c r="C6">
+        <v>5643</v>
+      </c>
+      <c r="D6">
+        <v>6798</v>
+      </c>
+      <c r="E6">
+        <v>7484</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7">
+        <v>171861</v>
+      </c>
+      <c r="C7">
+        <v>5643</v>
+      </c>
+      <c r="D7">
         <v>0</v>
       </c>
-      <c r="D3">
-        <v>25448</v>
-      </c>
-      <c r="E3">
+      <c r="E7">
+        <v>7484</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8">
+        <v>172979</v>
+      </c>
+      <c r="C8">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>28009</v>
-      </c>
-      <c r="G3">
-        <v>72521</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4">
-        <v>129329</v>
-      </c>
-      <c r="C4">
-        <v>19890</v>
-      </c>
-      <c r="D4">
-        <v>24115</v>
-      </c>
-      <c r="E4">
-        <v>31746</v>
-      </c>
-      <c r="F4">
-        <v>26533</v>
-      </c>
-      <c r="G4">
-        <v>68705</v>
-      </c>
-      <c r="H4">
-        <v>83034</v>
-      </c>
-      <c r="I4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5">
-        <v>171098</v>
-      </c>
-      <c r="C5">
-        <v>9945</v>
-      </c>
-      <c r="D5">
-        <v>12058</v>
-      </c>
-      <c r="E5">
-        <v>15873</v>
-      </c>
-      <c r="F5">
-        <v>13267</v>
-      </c>
-      <c r="G5">
-        <v>34353</v>
-      </c>
-      <c r="H5">
-        <v>41517</v>
-      </c>
-      <c r="I5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6">
-        <v>195833</v>
-      </c>
-      <c r="C6">
-        <v>9945</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>13267</v>
-      </c>
-      <c r="G6">
-        <v>34353</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7">
-        <v>191983</v>
-      </c>
-      <c r="C7">
-        <v>5558</v>
-      </c>
-      <c r="D7">
-        <v>6695</v>
-      </c>
-      <c r="E7">
-        <v>8821</v>
-      </c>
-      <c r="F7">
-        <v>7371</v>
-      </c>
-      <c r="G7">
-        <v>19084</v>
-      </c>
-      <c r="H7">
-        <v>23064</v>
-      </c>
-      <c r="I7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8">
-        <v>208415</v>
-      </c>
-      <c r="C8">
-        <v>5558</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7342,336 +11085,687 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>7371</v>
-      </c>
-      <c r="G8">
-        <v>19084</v>
-      </c>
-      <c r="H8">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD47A3B8-CE4B-466A-AE2C-4803543FDDCC}">
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="I8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>62242</v>
+      </c>
+      <c r="C2">
+        <v>69409</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>75677</v>
+      </c>
+      <c r="C3">
+        <v>83607</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>93409</v>
+      </c>
+      <c r="C4">
+        <v>104104</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>112034</v>
+      </c>
+      <c r="C5">
+        <v>124490</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>124490</v>
+      </c>
+      <c r="C6">
+        <v>138799</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7">
+        <v>93409</v>
+      </c>
+      <c r="C7">
+        <v>104104</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8">
+        <v>112034</v>
+      </c>
+      <c r="C8">
+        <v>155651</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="B9">
-        <v>206271</v>
+        <v>147597</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>163438</v>
       </c>
       <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="B10">
-        <v>190883</v>
+        <v>176514</v>
       </c>
       <c r="C10">
-        <v>9945</v>
+        <v>196174</v>
       </c>
       <c r="D10">
-        <v>12058</v>
-      </c>
-      <c r="E10">
-        <v>15873</v>
-      </c>
-      <c r="F10">
-        <v>13267</v>
-      </c>
-      <c r="G10">
-        <v>34353</v>
-      </c>
-      <c r="H10">
-        <v>41517</v>
-      </c>
-      <c r="I10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B11">
-        <v>201875</v>
+        <v>205456</v>
       </c>
       <c r="C11">
-        <v>5558</v>
+        <v>218606</v>
       </c>
       <c r="D11">
-        <v>6695</v>
-      </c>
-      <c r="E11">
-        <v>8821</v>
-      </c>
-      <c r="F11">
-        <v>7371</v>
-      </c>
-      <c r="G11">
-        <v>19084</v>
-      </c>
-      <c r="H11">
-        <v>23064</v>
-      </c>
-      <c r="I11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="B12">
-        <v>144718</v>
+        <v>219871</v>
       </c>
       <c r="C12">
-        <v>22230</v>
+        <v>240008</v>
       </c>
       <c r="D12">
-        <v>26780</v>
-      </c>
-      <c r="E12">
-        <v>35282</v>
-      </c>
-      <c r="F12">
-        <v>29484</v>
-      </c>
-      <c r="G12">
-        <v>76336</v>
-      </c>
-      <c r="H12">
-        <v>92257</v>
-      </c>
-      <c r="I12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B13">
-        <v>195280</v>
+        <v>224180</v>
       </c>
       <c r="C13">
-        <v>7001</v>
+        <v>261528</v>
       </c>
       <c r="D13">
-        <v>8483</v>
-      </c>
-      <c r="E13">
-        <v>11174</v>
-      </c>
-      <c r="F13">
-        <v>9360</v>
-      </c>
-      <c r="G13">
-        <v>24180</v>
-      </c>
-      <c r="H13">
-        <v>29219</v>
-      </c>
-      <c r="I13" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="B14">
-        <v>207370</v>
+        <v>104104</v>
       </c>
       <c r="C14">
-        <v>3868</v>
+        <v>115667</v>
       </c>
       <c r="D14">
-        <v>5356</v>
-      </c>
-      <c r="E14">
-        <v>7053</v>
-      </c>
-      <c r="F14">
-        <v>5896</v>
-      </c>
-      <c r="G14">
-        <v>15269</v>
-      </c>
-      <c r="H14">
-        <v>18446</v>
-      </c>
-      <c r="I14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="B15">
-        <v>223579</v>
+        <v>125469</v>
       </c>
       <c r="C15">
-        <v>3868</v>
+        <v>138818</v>
       </c>
       <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>5896</v>
-      </c>
-      <c r="G15">
-        <v>15269</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="B16">
-        <v>180990</v>
+        <v>151299</v>
       </c>
       <c r="C16">
-        <v>15477</v>
+        <v>160964</v>
       </c>
       <c r="D16">
-        <v>20085</v>
-      </c>
-      <c r="E16">
-        <v>26455</v>
-      </c>
-      <c r="F16">
-        <v>22113</v>
-      </c>
-      <c r="G16">
-        <v>57259</v>
-      </c>
-      <c r="H16">
-        <v>69199</v>
-      </c>
-      <c r="I16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="B17">
-        <v>150213</v>
+        <v>173501</v>
       </c>
       <c r="C17">
-        <v>15477</v>
+        <v>201723</v>
       </c>
       <c r="D17">
-        <v>20085</v>
-      </c>
-      <c r="E17">
-        <v>26455</v>
-      </c>
-      <c r="F17">
-        <v>22113</v>
-      </c>
-      <c r="G17">
-        <v>57259</v>
-      </c>
-      <c r="H17">
-        <v>69199</v>
-      </c>
-      <c r="I17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="B18">
-        <v>283039</v>
+        <v>192126</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>224180</v>
       </c>
       <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>211730</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>246599</v>
       </c>
       <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="s">
-        <v>127</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>231334</v>
+      </c>
+      <c r="C20">
+        <v>269043</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>105865</v>
+      </c>
+      <c r="C21">
+        <v>117422</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22">
+        <v>126350</v>
+      </c>
+      <c r="C22">
+        <v>140560</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
+        <v>158305</v>
+      </c>
+      <c r="C23">
+        <v>184958</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24">
+        <v>189472</v>
+      </c>
+      <c r="C24">
+        <v>221383</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25">
+        <v>211730</v>
+      </c>
+      <c r="C25">
+        <v>246599</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26">
+        <v>232209</v>
+      </c>
+      <c r="C26">
+        <v>270884</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27">
+        <v>252594</v>
+      </c>
+      <c r="C27">
+        <v>294252</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28">
+        <v>125469</v>
+      </c>
+      <c r="C28">
+        <v>138799</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>134980</v>
+      </c>
+      <c r="C29">
+        <v>153016</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>173501</v>
+      </c>
+      <c r="C30">
+        <v>201723</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31">
+        <v>207316</v>
+      </c>
+      <c r="C31">
+        <v>241967</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32">
+        <v>209808</v>
+      </c>
+      <c r="C32">
+        <v>269043</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33">
+        <v>253487</v>
+      </c>
+      <c r="C33">
+        <v>295188</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34">
+        <v>267139</v>
+      </c>
+      <c r="C34">
+        <v>322245</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35">
+        <v>149482</v>
+      </c>
+      <c r="C35">
+        <v>166352</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36">
+        <v>180563</v>
+      </c>
+      <c r="C36">
+        <v>200167</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37">
+        <v>209076</v>
+      </c>
+      <c r="C37">
+        <v>248254</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38">
+        <v>221204</v>
+      </c>
+      <c r="C38">
+        <v>261528</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39">
+        <v>243325</v>
+      </c>
+      <c r="C39">
+        <v>280259</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40">
+        <v>267666</v>
+      </c>
+      <c r="C40">
+        <v>308252</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41">
+        <v>288288</v>
+      </c>
+      <c r="C41">
+        <v>336245</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42">
+        <v>192126</v>
+      </c>
+      <c r="C42">
+        <v>224167</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43">
+        <v>230355</v>
+      </c>
+      <c r="C43">
+        <v>231334</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44">
+        <v>259371</v>
+      </c>
+      <c r="C44">
+        <v>307328</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45">
+        <v>276625</v>
+      </c>
+      <c r="C45">
+        <v>320304</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46">
+        <v>292305</v>
+      </c>
+      <c r="C46">
+        <v>340988</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47">
+        <v>320242</v>
+      </c>
+      <c r="C47">
+        <v>373538</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48">
+        <v>336319</v>
+      </c>
+      <c r="C48">
+        <v>392348</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\German\Documents\sebamarapp\backend\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sebamar-cotizador\backend\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1340FFE0-34BD-43AB-A1F4-52761D7A2D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="939" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="260">
   <si>
     <t>MEDIDA</t>
   </si>
@@ -826,7 +825,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1140,14 +1139,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.3984375" style="1"/>
+    <col min="1" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1164,7 +1163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1181,7 +1180,7 @@
         <v>2556</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1198,7 +1197,7 @@
         <v>3570</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1215,7 +1214,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1232,7 +1231,7 @@
         <v>5622</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1249,7 +1248,7 @@
         <v>7140</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1266,7 +1265,7 @@
         <v>8676</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1283,7 +1282,7 @@
         <v>9696</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1300,7 +1299,7 @@
         <v>4254</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1317,7 +1316,7 @@
         <v>5952</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1334,7 +1333,7 @@
         <v>7656</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1351,7 +1350,7 @@
         <v>9354</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1368,7 +1367,7 @@
         <v>11910</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1385,7 +1384,7 @@
         <v>14460</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1402,7 +1401,7 @@
         <v>16158</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1419,7 +1418,7 @@
         <v>10716</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,7 +1435,7 @@
         <v>13098</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1453,7 +1452,7 @@
         <v>16668</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1470,7 +1469,7 @@
         <v>20244</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1487,7 +1486,7 @@
         <v>22620</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -1504,7 +1503,7 @@
         <v>13776</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1521,7 +1520,7 @@
         <v>16842</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -1538,7 +1537,7 @@
         <v>21432</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1555,7 +1554,7 @@
         <v>26022</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1572,7 +1571,7 @@
         <v>29088</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1589,7 +1588,7 @@
         <v>32148</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -1606,7 +1605,7 @@
         <v>35208</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -1623,7 +1622,7 @@
         <v>15312</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -1640,7 +1639,7 @@
         <v>18708</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -1657,7 +1656,7 @@
         <v>23814</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1674,392 +1673,411 @@
         <v>28920</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+        <v>163</v>
+      </c>
+      <c r="B32" s="1">
+        <v>81200</v>
+      </c>
+      <c r="C32" s="1">
+        <v>18929</v>
+      </c>
+      <c r="D32" s="1">
+        <v>39514</v>
+      </c>
+      <c r="E32" s="1">
+        <v>35718</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+        <v>164</v>
+      </c>
+      <c r="B33" s="1">
+        <v>81200</v>
+      </c>
+      <c r="C33" s="1">
+        <v>18929</v>
+      </c>
+      <c r="D33" s="1">
+        <v>39514</v>
+      </c>
+      <c r="E33" s="1">
+        <v>39120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+      <c r="B34" s="1">
+        <v>59233</v>
+      </c>
+      <c r="C34" s="1">
+        <v>20650</v>
+      </c>
+      <c r="D34" s="1">
+        <v>24998</v>
+      </c>
+      <c r="E34" s="1">
+        <v>16842</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35" s="1">
-        <v>59233</v>
+        <v>62714</v>
       </c>
       <c r="C35" s="1">
         <v>20650</v>
       </c>
       <c r="D35" s="1">
-        <v>24998</v>
+        <v>27418</v>
       </c>
       <c r="E35" s="1">
-        <v>16842</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+        <v>20580</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" s="1">
-        <v>62714</v>
+        <v>68494</v>
       </c>
       <c r="C36" s="1">
         <v>20650</v>
       </c>
       <c r="D36" s="1">
-        <v>27418</v>
+        <v>31046</v>
       </c>
       <c r="E36" s="1">
-        <v>20580</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+        <v>26196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="1">
-        <v>68494</v>
+        <v>73158</v>
       </c>
       <c r="C37" s="1">
         <v>20650</v>
       </c>
       <c r="D37" s="1">
-        <v>31046</v>
+        <v>34675</v>
       </c>
       <c r="E37" s="1">
-        <v>26196</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+        <v>31806</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1">
-        <v>73158</v>
+        <v>79937</v>
       </c>
       <c r="C38" s="1">
         <v>20650</v>
       </c>
       <c r="D38" s="1">
-        <v>34675</v>
+        <v>37094</v>
       </c>
       <c r="E38" s="1">
-        <v>31806</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+        <v>35550</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" s="1">
-        <v>79937</v>
+        <v>83467</v>
       </c>
       <c r="C39" s="1">
         <v>20650</v>
       </c>
       <c r="D39" s="1">
-        <v>37094</v>
+        <v>39514</v>
       </c>
       <c r="E39" s="1">
-        <v>35550</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+        <v>39294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="1">
-        <v>83467</v>
+        <v>85547</v>
       </c>
       <c r="C40" s="1">
         <v>20650</v>
       </c>
       <c r="D40" s="1">
-        <v>39514</v>
+        <v>41933</v>
       </c>
       <c r="E40" s="1">
-        <v>39294</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+        <v>43038</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="1">
-        <v>85547</v>
+        <v>67529</v>
       </c>
       <c r="C41" s="1">
-        <v>20650</v>
+        <v>25813</v>
       </c>
       <c r="D41" s="1">
-        <v>41933</v>
+        <v>29904</v>
       </c>
       <c r="E41" s="1">
-        <v>43038</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+        <v>21432</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="1">
-        <v>67529</v>
+        <v>71011</v>
       </c>
       <c r="C42" s="1">
         <v>25813</v>
       </c>
       <c r="D42" s="1">
-        <v>29904</v>
+        <v>32659</v>
       </c>
       <c r="E42" s="1">
-        <v>21432</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+        <v>26196</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" s="1">
-        <v>71011</v>
+        <v>76790</v>
       </c>
       <c r="C43" s="1">
         <v>25813</v>
       </c>
       <c r="D43" s="1">
-        <v>32659</v>
+        <v>36792</v>
       </c>
       <c r="E43" s="1">
-        <v>26196</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+        <v>33336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" s="1">
-        <v>76790</v>
+        <v>80340</v>
       </c>
       <c r="C44" s="1">
         <v>25813</v>
       </c>
       <c r="D44" s="1">
-        <v>36792</v>
+        <v>40925</v>
       </c>
       <c r="E44" s="1">
-        <v>33336</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+        <v>40482</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" s="1">
-        <v>80340</v>
+        <v>87942</v>
       </c>
       <c r="C45" s="1">
         <v>25813</v>
       </c>
       <c r="D45" s="1">
-        <v>40925</v>
+        <v>43680</v>
       </c>
       <c r="E45" s="1">
-        <v>40482</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+        <v>45246</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B46" s="1">
-        <v>87942</v>
+        <v>90649</v>
       </c>
       <c r="C46" s="1">
         <v>25813</v>
       </c>
       <c r="D46" s="1">
-        <v>43680</v>
+        <v>46435</v>
       </c>
       <c r="E46" s="1">
-        <v>45246</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+        <v>50004</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" s="1">
-        <v>90649</v>
+        <v>94129</v>
       </c>
       <c r="C47" s="1">
         <v>25813</v>
       </c>
       <c r="D47" s="1">
-        <v>46435</v>
+        <v>49190</v>
       </c>
       <c r="E47" s="1">
-        <v>50004</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+        <v>54774</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48" s="1">
-        <v>94129</v>
+        <v>86650</v>
       </c>
       <c r="C48" s="1">
-        <v>25813</v>
+        <v>34418</v>
       </c>
       <c r="D48" s="1">
-        <v>49190</v>
+        <v>38080</v>
       </c>
       <c r="E48" s="1">
-        <v>54774</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+        <v>29088</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49" s="1">
-        <v>86650</v>
+        <v>92782</v>
       </c>
       <c r="C49" s="1">
         <v>34418</v>
       </c>
       <c r="D49" s="1">
-        <v>38080</v>
+        <v>41395</v>
       </c>
       <c r="E49" s="1">
-        <v>29088</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+        <v>35550</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B50" s="1">
-        <v>92782</v>
+        <v>101660</v>
       </c>
       <c r="C50" s="1">
         <v>34418</v>
       </c>
       <c r="D50" s="1">
-        <v>41395</v>
+        <v>46368</v>
       </c>
       <c r="E50" s="1">
-        <v>35550</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+        <v>47628</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51" s="1">
-        <v>101660</v>
+        <v>109037</v>
       </c>
       <c r="C51" s="1">
         <v>34418</v>
       </c>
       <c r="D51" s="1">
-        <v>46368</v>
+        <v>51341</v>
       </c>
       <c r="E51" s="1">
-        <v>47628</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+        <v>57834</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52" s="1">
-        <v>109037</v>
+        <v>116081</v>
       </c>
       <c r="C52" s="1">
         <v>34418</v>
       </c>
       <c r="D52" s="1">
-        <v>51341</v>
+        <v>54656</v>
       </c>
       <c r="E52" s="1">
-        <v>57834</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+        <v>64638</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53" s="1">
-        <v>116081</v>
+        <v>123055</v>
       </c>
       <c r="C53" s="1">
         <v>34418</v>
       </c>
       <c r="D53" s="1">
-        <v>54656</v>
+        <v>57971</v>
       </c>
       <c r="E53" s="1">
-        <v>64638</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+        <v>71442</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54" s="1">
-        <v>123055</v>
+        <v>127846</v>
       </c>
       <c r="C54" s="1">
         <v>34418</v>
       </c>
       <c r="D54" s="1">
-        <v>57971</v>
+        <v>61286</v>
       </c>
       <c r="E54" s="1">
-        <v>71442</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+        <v>78246</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B55" s="1">
-        <v>127846</v>
+        <v>134238</v>
       </c>
       <c r="C55" s="1">
-        <v>34418</v>
+        <v>36139</v>
       </c>
       <c r="D55" s="1">
-        <v>61286</v>
+        <v>64350</v>
       </c>
       <c r="E55" s="1">
-        <v>78246</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A56" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" s="1">
-        <v>134238</v>
-      </c>
-      <c r="C56" s="1">
-        <v>36139</v>
-      </c>
-      <c r="D56" s="1">
-        <v>64350</v>
-      </c>
-      <c r="E56" s="1">
         <v>82158</v>
       </c>
     </row>
@@ -2069,11 +2087,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE426D2-2546-4C09-9E49-393CA4A2B16B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>165</v>
       </c>
@@ -2093,7 +2111,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>168</v>
       </c>
@@ -2113,7 +2131,7 @@
         <v>61992</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>168</v>
       </c>
@@ -2133,7 +2151,7 @@
         <v>69741</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>168</v>
       </c>
@@ -2153,7 +2171,7 @@
         <v>77490</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -2173,7 +2191,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>168</v>
       </c>
@@ -2193,7 +2211,7 @@
         <v>67158</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>168</v>
       </c>
@@ -2213,7 +2231,7 @@
         <v>72324</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>168</v>
       </c>
@@ -2233,7 +2251,7 @@
         <v>80073</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>168</v>
       </c>
@@ -2253,7 +2271,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>168</v>
       </c>
@@ -2273,7 +2291,7 @@
         <v>92988</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>168</v>
       </c>
@@ -2293,7 +2311,7 @@
         <v>77490</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>168</v>
       </c>
@@ -2313,7 +2331,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>168</v>
       </c>
@@ -2333,7 +2351,7 @@
         <v>90405</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -2353,7 +2371,7 @@
         <v>98154</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>168</v>
       </c>
@@ -2373,7 +2391,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>168</v>
       </c>
@@ -2393,7 +2411,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>168</v>
       </c>
@@ -2413,7 +2431,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>168</v>
       </c>
@@ -2433,7 +2451,7 @@
         <v>95571</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -2453,7 +2471,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -2473,7 +2491,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>168</v>
       </c>
@@ -2493,7 +2511,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>168</v>
       </c>
@@ -2513,7 +2531,7 @@
         <v>92988</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -2533,7 +2551,7 @@
         <v>100737</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>168</v>
       </c>
@@ -2553,7 +2571,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>168</v>
       </c>
@@ -2573,7 +2591,7 @@
         <v>113652</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>168</v>
       </c>
@@ -2593,7 +2611,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>168</v>
       </c>
@@ -2613,7 +2631,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>168</v>
       </c>
@@ -2633,7 +2651,7 @@
         <v>116235</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>168</v>
       </c>
@@ -2653,7 +2671,7 @@
         <v>123984</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>168</v>
       </c>
@@ -2673,7 +2691,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>169</v>
       </c>
@@ -2693,7 +2711,7 @@
         <v>98154</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>169</v>
       </c>
@@ -2713,7 +2731,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>169</v>
       </c>
@@ -2739,11 +2757,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEBDCEAF-E769-44C4-B34F-C931B2DDA697}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2751,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -2759,7 +2777,7 @@
         <v>11094</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -2767,7 +2785,7 @@
         <v>12830</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -2775,7 +2793,7 @@
         <v>14565</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -2783,7 +2801,7 @@
         <v>16300</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>171</v>
       </c>
@@ -2791,7 +2809,7 @@
         <v>18905</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>172</v>
       </c>
@@ -2799,7 +2817,7 @@
         <v>21508</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>173</v>
       </c>
@@ -2807,7 +2825,7 @@
         <v>23244</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -2815,7 +2833,7 @@
         <v>17580</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2823,7 +2841,7 @@
         <v>19772</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2831,7 +2849,7 @@
         <v>21965</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2839,7 +2857,7 @@
         <v>25254</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -2847,7 +2865,7 @@
         <v>28542</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2855,7 +2873,7 @@
         <v>30736</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>174</v>
       </c>
@@ -2863,7 +2881,7 @@
         <v>32927</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>175</v>
       </c>
@@ -2871,7 +2889,7 @@
         <v>35120</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -2879,7 +2897,7 @@
         <v>21508</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>156</v>
       </c>
@@ -2887,7 +2905,7 @@
         <v>23853</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>157</v>
       </c>
@@ -2895,7 +2913,7 @@
         <v>27371</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>158</v>
       </c>
@@ -2903,7 +2921,7 @@
         <v>30887</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>159</v>
       </c>
@@ -2911,7 +2929,7 @@
         <v>33232</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>160</v>
       </c>
@@ -2919,7 +2937,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>161</v>
       </c>
@@ -2927,7 +2945,7 @@
         <v>37923</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2935,7 +2953,7 @@
         <v>24980</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2943,7 +2961,7 @@
         <v>27630</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2951,7 +2969,7 @@
         <v>31603</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2959,7 +2977,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>162</v>
       </c>
@@ -2967,7 +2985,7 @@
         <v>38227</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>163</v>
       </c>
@@ -2975,7 +2993,7 @@
         <v>40877</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>164</v>
       </c>
@@ -2983,7 +3001,7 @@
         <v>43526</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>176</v>
       </c>
@@ -2991,7 +3009,7 @@
         <v>31405</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -2999,7 +3017,7 @@
         <v>35836</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>178</v>
       </c>
@@ -3007,7 +3025,7 @@
         <v>40268</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -3015,7 +3033,7 @@
         <v>43221</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>180</v>
       </c>
@@ -3023,7 +3041,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>181</v>
       </c>
@@ -3031,7 +3049,7 @@
         <v>49130</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -3039,7 +3057,7 @@
         <v>32982</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -3047,7 +3065,7 @@
         <v>37565</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -3055,7 +3073,7 @@
         <v>42148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -3063,7 +3081,7 @@
         <v>45203</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -3071,7 +3089,7 @@
         <v>48257</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -3079,7 +3097,7 @@
         <v>51313</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -3087,7 +3105,7 @@
         <v>38292</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>183</v>
       </c>
@@ -3095,7 +3113,7 @@
         <v>43518</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>184</v>
       </c>
@@ -3103,7 +3121,7 @@
         <v>48743</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>185</v>
       </c>
@@ -3111,7 +3129,7 @@
         <v>52226</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>186</v>
       </c>
@@ -3119,7 +3137,7 @@
         <v>55709</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>187</v>
       </c>
@@ -3127,7 +3145,7 @@
         <v>59193</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -3135,7 +3153,7 @@
         <v>41832</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -3143,7 +3161,7 @@
         <v>47486</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -3151,7 +3169,7 @@
         <v>53139</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -3159,7 +3177,7 @@
         <v>56908</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -3167,7 +3185,7 @@
         <v>60677</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -3175,7 +3193,7 @@
         <v>64446</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -3189,11 +3207,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A9F9EE-BDDB-4579-BA1F-FD3339C134CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>165</v>
       </c>
@@ -3213,7 +3231,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>191</v>
       </c>
@@ -3230,7 +3248,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>191</v>
       </c>
@@ -3247,7 +3265,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>191</v>
       </c>
@@ -3264,7 +3282,7 @@
         <v>70100</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>191</v>
       </c>
@@ -3281,7 +3299,7 @@
         <v>117180</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>191</v>
       </c>
@@ -3298,7 +3316,7 @@
         <v>117180</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>191</v>
       </c>
@@ -3315,7 +3333,7 @@
         <v>122300</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>191</v>
       </c>
@@ -3332,7 +3350,7 @@
         <v>204498</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -3349,7 +3367,7 @@
         <v>204498</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>191</v>
       </c>
@@ -3366,7 +3384,7 @@
         <v>208575</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>191</v>
       </c>
@@ -3380,7 +3398,7 @@
         <v>64350</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>191</v>
       </c>
@@ -3394,7 +3412,7 @@
         <v>64350</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>191</v>
       </c>
@@ -3408,7 +3426,7 @@
         <v>67260</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>191</v>
       </c>
@@ -3422,7 +3440,7 @@
         <v>133075</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>191</v>
       </c>
@@ -3436,7 +3454,7 @@
         <v>133875</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>191</v>
       </c>
@@ -3450,7 +3468,7 @@
         <v>145763</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>200</v>
       </c>
@@ -3467,7 +3485,7 @@
         <v>174350</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>200</v>
       </c>
@@ -3484,7 +3502,7 @@
         <v>174350</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>200</v>
       </c>
@@ -3501,7 +3519,7 @@
         <v>186300</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>200</v>
       </c>
@@ -3518,7 +3536,7 @@
         <v>206731</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>200</v>
       </c>
@@ -3535,7 +3553,7 @@
         <v>206731</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>200</v>
       </c>
@@ -3552,7 +3570,7 @@
         <v>208285</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>200</v>
       </c>
@@ -3569,7 +3587,7 @@
         <v>271005</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>200</v>
       </c>
@@ -3586,7 +3604,7 @@
         <v>271005</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>200</v>
       </c>
@@ -3609,11 +3627,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A83AEA-1664-4235-A07C-8B238DD223C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>202</v>
       </c>
@@ -3627,7 +3645,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -3638,7 +3656,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>206</v>
       </c>
@@ -3649,7 +3667,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>206</v>
       </c>
@@ -3660,7 +3678,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>206</v>
       </c>
@@ -3671,7 +3689,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>206</v>
       </c>
@@ -3682,7 +3700,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>206</v>
       </c>
@@ -3693,7 +3711,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>218</v>
       </c>
@@ -3707,7 +3725,7 @@
         <v>10685</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>218</v>
       </c>
@@ -3721,7 +3739,7 @@
         <v>20505</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>218</v>
       </c>
@@ -3732,7 +3750,7 @@
         <v>7400</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>218</v>
       </c>
@@ -3743,7 +3761,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>218</v>
       </c>
@@ -3757,7 +3775,7 @@
         <v>13517</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>218</v>
       </c>
@@ -3771,7 +3789,7 @@
         <v>20505</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>218</v>
       </c>
@@ -3782,7 +3800,7 @@
         <v>5905</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>218</v>
       </c>
@@ -3793,7 +3811,7 @@
         <v>48364</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>218</v>
       </c>
@@ -3804,7 +3822,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>218</v>
       </c>
@@ -3818,7 +3836,7 @@
         <v>18500</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>218</v>
       </c>
@@ -3832,7 +3850,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>230</v>
       </c>
@@ -3843,7 +3861,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>230</v>
       </c>
@@ -3854,7 +3872,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>230</v>
       </c>
@@ -3865,7 +3883,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>230</v>
       </c>
@@ -3876,7 +3894,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>230</v>
       </c>
@@ -3887,7 +3905,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>230</v>
       </c>
@@ -3898,7 +3916,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>230</v>
       </c>
@@ -3909,7 +3927,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>238</v>
       </c>
@@ -3920,7 +3938,7 @@
         <v>16500</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>238</v>
       </c>
@@ -3931,7 +3949,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>241</v>
       </c>
@@ -3942,7 +3960,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>241</v>
       </c>
@@ -3953,7 +3971,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>241</v>
       </c>
@@ -3964,7 +3982,7 @@
         <v>850000</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>241</v>
       </c>
@@ -3975,7 +3993,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>241</v>
       </c>
@@ -3986,7 +4004,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>241</v>
       </c>
@@ -4000,7 +4018,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>241</v>
       </c>
@@ -4014,7 +4032,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>241</v>
       </c>
@@ -4025,7 +4043,7 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>241</v>
       </c>
@@ -4039,7 +4057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>241</v>
       </c>
@@ -4053,7 +4071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>249</v>
       </c>
@@ -4064,7 +4082,7 @@
         <v>101970</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>249</v>
       </c>
@@ -4075,7 +4093,7 @@
         <v>112167</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -4086,7 +4104,7 @@
         <v>16459</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -4097,7 +4115,7 @@
         <v>21250</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -4108,7 +4126,7 @@
         <v>27169</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -4119,7 +4137,7 @@
         <v>33410</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -4130,7 +4148,7 @@
         <v>27012</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -4141,7 +4159,7 @@
         <v>60797</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -4152,7 +4170,7 @@
         <v>65546</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -4163,7 +4181,7 @@
         <v>73221</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -4174,7 +4192,7 @@
         <v>88575</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -4191,11 +4209,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82512D28-CBA6-44C4-BB91-2A44CD2A0064}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>253</v>
       </c>
@@ -4203,7 +4221,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>215</v>
       </c>
@@ -4211,7 +4229,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>255</v>
       </c>
@@ -4219,7 +4237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>256</v>
       </c>
@@ -4227,7 +4245,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>258</v>
       </c>
@@ -4241,14 +4259,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.3984375" style="1"/>
+    <col min="1" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4277,7 +4295,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4306,7 +4324,7 @@
         <v>36118</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -4335,7 +4353,7 @@
         <v>41278</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -4364,7 +4382,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -4393,7 +4411,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -4422,7 +4440,7 @@
         <v>59337</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -4451,7 +4469,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -4480,7 +4498,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -4509,7 +4527,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -4538,7 +4556,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -4567,7 +4585,7 @@
         <v>56757</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -4596,7 +4614,7 @@
         <v>61916</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -4625,7 +4643,7 @@
         <v>69656</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -4654,7 +4672,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -4683,7 +4701,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -4712,7 +4730,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -4741,7 +4759,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -4770,7 +4788,7 @@
         <v>79975</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -4799,7 +4817,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -4828,7 +4846,7 @@
         <v>92875</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -4857,7 +4875,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -4886,7 +4904,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -4915,7 +4933,7 @@
         <v>90295</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -4944,7 +4962,7 @@
         <v>98034</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -4973,7 +4991,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -5002,7 +5020,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -5031,7 +5049,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -5060,7 +5078,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -5089,7 +5107,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -5118,7 +5136,7 @@
         <v>95454</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -5147,7 +5165,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>163</v>
       </c>
@@ -5176,7 +5194,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>164</v>
       </c>
@@ -5205,7 +5223,7 @@
         <v>118673</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -5234,7 +5252,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -5263,7 +5281,7 @@
         <v>92875</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -5292,7 +5310,7 @@
         <v>100614</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -5321,7 +5339,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -5350,7 +5368,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -5379,7 +5397,7 @@
         <v>118673</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -5408,7 +5426,7 @@
         <v>123833</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -5437,7 +5455,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -5466,7 +5484,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -5495,7 +5513,7 @@
         <v>116093</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -5524,7 +5542,7 @@
         <v>123833</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,7 +5571,7 @@
         <v>128993</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -5582,7 +5600,7 @@
         <v>134152</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -5611,7 +5629,7 @@
         <v>139312</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -5640,7 +5658,7 @@
         <v>128993</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
@@ -5669,7 +5687,7 @@
         <v>134152</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -5698,7 +5716,7 @@
         <v>141892</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -5727,7 +5745,7 @@
         <v>149631</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -5756,7 +5774,7 @@
         <v>154791</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
@@ -5785,7 +5803,7 @@
         <v>159951</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -5814,7 +5832,7 @@
         <v>165110</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -5850,11 +5868,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5880,7 +5898,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -5906,7 +5924,7 @@
         <v>12649</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -5932,7 +5950,7 @@
         <v>16877</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -5958,7 +5976,7 @@
         <v>21105</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -5984,7 +6002,7 @@
         <v>25332</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6010,7 +6028,7 @@
         <v>29560</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -6036,7 +6054,7 @@
         <v>33788</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6062,7 +6080,7 @@
         <v>38016</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -6088,7 +6106,7 @@
         <v>16877</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -6114,7 +6132,7 @@
         <v>22499</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -6140,7 +6158,7 @@
         <v>28120</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -6166,7 +6184,7 @@
         <v>33742</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -6192,7 +6210,7 @@
         <v>39364</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -6218,7 +6236,7 @@
         <v>44986</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -6244,7 +6262,7 @@
         <v>50607</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -6270,7 +6288,7 @@
         <v>21105</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -6296,7 +6314,7 @@
         <v>28120</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -6322,7 +6340,7 @@
         <v>35136</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -6348,7 +6366,7 @@
         <v>42152</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -6374,7 +6392,7 @@
         <v>49167</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -6400,7 +6418,7 @@
         <v>56183</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -6426,7 +6444,7 @@
         <v>63199</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -6452,7 +6470,7 @@
         <v>25332</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -6478,7 +6496,7 @@
         <v>33742</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -6504,7 +6522,7 @@
         <v>42152</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -6530,7 +6548,7 @@
         <v>50561</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -6556,7 +6574,7 @@
         <v>58971</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -6582,7 +6600,7 @@
         <v>67380</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -6608,7 +6626,7 @@
         <v>75790</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -6634,7 +6652,7 @@
         <v>29560</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -6660,7 +6678,7 @@
         <v>39364</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -6686,7 +6704,7 @@
         <v>58971</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -6712,7 +6730,7 @@
         <v>68774</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -6738,7 +6756,7 @@
         <v>78578</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -6764,7 +6782,7 @@
         <v>88381</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -6790,7 +6808,7 @@
         <v>33788</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -6816,7 +6834,7 @@
         <v>44986</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -6842,7 +6860,7 @@
         <v>56183</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -6868,7 +6886,7 @@
         <v>67380</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -6894,7 +6912,7 @@
         <v>78578</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -6920,7 +6938,7 @@
         <v>89775</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -6946,7 +6964,7 @@
         <v>100973</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -6972,7 +6990,7 @@
         <v>38016</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -6998,7 +7016,7 @@
         <v>50607</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -7024,7 +7042,7 @@
         <v>63199</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -7050,7 +7068,7 @@
         <v>75790</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -7076,7 +7094,7 @@
         <v>88381</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -7102,7 +7120,7 @@
         <v>100973</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -7128,7 +7146,7 @@
         <v>113564</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -7154,7 +7172,7 @@
         <v>42175</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -7180,7 +7198,7 @@
         <v>56241</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -7206,7 +7224,7 @@
         <v>70307</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -7232,7 +7250,7 @@
         <v>84372</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -7258,7 +7276,7 @@
         <v>98438</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -7284,7 +7302,7 @@
         <v>112504</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -7310,7 +7328,7 @@
         <v>126570</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -7336,7 +7354,7 @@
         <v>46391</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -7362,7 +7380,7 @@
         <v>61862</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -7388,7 +7406,7 @@
         <v>77334</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -7414,7 +7432,7 @@
         <v>92805</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -7440,7 +7458,7 @@
         <v>108276</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -7466,7 +7484,7 @@
         <v>123748</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>35</v>
       </c>
@@ -7492,7 +7510,7 @@
         <v>139219</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -7518,7 +7536,7 @@
         <v>59052</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -7544,7 +7562,7 @@
         <v>78728</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -7570,7 +7588,7 @@
         <v>98404</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -7596,7 +7614,7 @@
         <v>118080</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -7622,7 +7640,7 @@
         <v>130499</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -7648,7 +7666,7 @@
         <v>142917</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -7680,11 +7698,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7713,7 +7731,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -7742,7 +7760,7 @@
         <v>24806</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -7771,7 +7789,7 @@
         <v>27907</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -7800,7 +7818,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -7829,7 +7847,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -7858,7 +7876,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -7887,7 +7905,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -7916,7 +7934,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -7945,7 +7963,7 @@
         <v>27907</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -7974,7 +7992,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -8003,7 +8021,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -8032,7 +8050,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -8061,7 +8079,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -8090,7 +8108,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -8119,7 +8137,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -8148,7 +8166,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -8177,7 +8195,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -8206,7 +8224,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -8235,7 +8253,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -8264,7 +8282,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -8293,7 +8311,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -8322,7 +8340,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -8351,7 +8369,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -8380,7 +8398,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -8409,7 +8427,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -8438,7 +8456,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -8467,7 +8485,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -8496,7 +8514,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -8525,7 +8543,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -8554,7 +8572,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -8583,7 +8601,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -8612,7 +8630,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -8641,7 +8659,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -8670,7 +8688,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -8699,7 +8717,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -8728,7 +8746,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -8757,7 +8775,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -8786,7 +8804,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -8815,7 +8833,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -8844,7 +8862,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -8873,7 +8891,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -8902,7 +8920,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -8931,7 +8949,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -8960,7 +8978,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -8989,7 +9007,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -9018,7 +9036,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -9047,7 +9065,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -9076,7 +9094,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -9105,7 +9123,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -9134,7 +9152,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -9163,7 +9181,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -9192,7 +9210,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -9221,7 +9239,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -9250,7 +9268,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -9279,7 +9297,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -9308,7 +9326,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -9337,7 +9355,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -9366,7 +9384,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -9395,7 +9413,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -9424,7 +9442,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -9453,7 +9471,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -9482,7 +9500,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>35</v>
       </c>
@@ -9511,7 +9529,7 @@
         <v>68218</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -9540,7 +9558,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -9569,7 +9587,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -9598,7 +9616,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -9627,7 +9645,7 @@
         <v>68218</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -9656,7 +9674,7 @@
         <v>71318</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -9685,7 +9703,7 @@
         <v>74419</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -9720,11 +9738,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -9750,7 +9768,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -9776,7 +9794,7 @@
         <v>108521</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -9802,7 +9820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -9828,7 +9846,7 @@
         <v>83034</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -9854,7 +9872,7 @@
         <v>41517</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -9880,7 +9898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -9906,7 +9924,7 @@
         <v>23064</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -9932,7 +9950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -9958,7 +9976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -9984,7 +10002,7 @@
         <v>41517</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -10010,7 +10028,7 @@
         <v>23064</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -10036,7 +10054,7 @@
         <v>92257</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -10062,7 +10080,7 @@
         <v>29219</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -10088,7 +10106,7 @@
         <v>18446</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -10114,7 +10132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -10140,7 +10158,7 @@
         <v>69199</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -10166,7 +10184,7 @@
         <v>69199</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>141</v>
       </c>
@@ -10192,7 +10210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>142</v>
       </c>
@@ -10224,11 +10242,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783F635A-904E-4A2A-ABB3-ADAB2016D027}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -10248,7 +10266,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>143</v>
       </c>
@@ -10268,7 +10286,7 @@
         <v>48354</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -10288,7 +10306,7 @@
         <v>48354</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -10308,7 +10326,7 @@
         <v>38175</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -10328,7 +10346,7 @@
         <v>38175</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>147</v>
       </c>
@@ -10348,7 +10366,7 @@
         <v>25448</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -10368,7 +10386,7 @@
         <v>25448</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -10388,7 +10406,7 @@
         <v>63622</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -10414,11 +10432,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE0A675-4F8B-4A13-BCE1-53842A29437E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -10447,7 +10465,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -10476,7 +10494,7 @@
         <v>70560</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -10505,7 +10523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -10534,7 +10552,7 @@
         <v>90720</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -10563,7 +10581,7 @@
         <v>45360</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -10592,7 +10610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -10621,7 +10639,7 @@
         <v>32760</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -10650,7 +10668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -10679,7 +10697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -10708,7 +10726,7 @@
         <v>95760</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -10737,7 +10755,7 @@
         <v>57960</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -10766,7 +10784,7 @@
         <v>131040</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -10795,7 +10813,7 @@
         <v>59220</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -10824,7 +10842,7 @@
         <v>34020</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -10853,7 +10871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -10882,7 +10900,7 @@
         <v>133560</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -10911,7 +10929,7 @@
         <v>57960</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -10946,11 +10964,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD041F75-528C-4B17-92E2-D6C4283D27D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -10967,7 +10985,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -10984,7 +11002,7 @@
         <v>28439</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -11001,7 +11019,7 @@
         <v>26941</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -11018,7 +11036,7 @@
         <v>13471</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>152</v>
       </c>
@@ -11035,7 +11053,7 @@
         <v>13471</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -11052,7 +11070,7 @@
         <v>7484</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -11069,7 +11087,7 @@
         <v>7484</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -11092,11 +11110,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD47A3B8-CE4B-466A-AE2C-4803543FDDCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11110,7 +11128,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -11124,7 +11142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -11138,7 +11156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -11152,7 +11170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -11166,7 +11184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -11180,7 +11198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>97</v>
       </c>
@@ -11194,7 +11212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>156</v>
       </c>
@@ -11208,7 +11226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>157</v>
       </c>
@@ -11222,7 +11240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>158</v>
       </c>
@@ -11236,7 +11254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>159</v>
       </c>
@@ -11250,7 +11268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>160</v>
       </c>
@@ -11264,7 +11282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>161</v>
       </c>
@@ -11278,7 +11296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -11292,7 +11310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -11306,7 +11324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -11320,7 +11338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -11334,7 +11352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -11348,7 +11366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -11362,7 +11380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -11376,7 +11394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -11390,7 +11408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -11404,7 +11422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -11418,7 +11436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -11432,7 +11450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>162</v>
       </c>
@@ -11446,7 +11464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>163</v>
       </c>
@@ -11460,7 +11478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>164</v>
       </c>
@@ -11474,7 +11492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -11488,7 +11506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -11502,7 +11520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -11516,7 +11534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -11530,7 +11548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -11544,7 +11562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -11558,7 +11576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -11572,7 +11590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -11586,7 +11604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -11600,7 +11618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -11614,7 +11632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -11628,7 +11646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -11642,7 +11660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -11656,7 +11674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -11670,7 +11688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -11684,7 +11702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -11698,7 +11716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -11712,7 +11730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -11726,7 +11744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -11740,7 +11758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -11754,7 +11772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>55</v>
       </c>

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939" firstSheet="2" activeTab="11"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939" firstSheet="8" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>
@@ -3253,7 +3253,9 @@
   <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="21" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3290,10 +3292,10 @@
         <v>193</v>
       </c>
       <c r="D2" s="1">
-        <v>62100</v>
+        <v>76300</v>
       </c>
       <c r="E2" s="1">
-        <v>66000</v>
+        <v>81100</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3307,10 +3309,10 @@
         <v>194</v>
       </c>
       <c r="D3" s="1">
-        <v>62100</v>
+        <v>76300</v>
       </c>
       <c r="E3" s="1">
-        <v>66000</v>
+        <v>81100</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3324,10 +3326,10 @@
         <v>195</v>
       </c>
       <c r="D4" s="1">
-        <v>66000</v>
+        <v>81100</v>
       </c>
       <c r="E4" s="1">
-        <v>70100</v>
+        <v>86112</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3341,10 +3343,10 @@
         <v>193</v>
       </c>
       <c r="D5" s="1">
-        <v>112717</v>
+        <v>138500</v>
       </c>
       <c r="E5" s="1">
-        <v>117180</v>
+        <v>144100</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,10 +3360,10 @@
         <v>194</v>
       </c>
       <c r="D6" s="1">
-        <v>112717</v>
+        <v>138500</v>
       </c>
       <c r="E6" s="1">
-        <v>117180</v>
+        <v>144100</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3375,10 +3377,10 @@
         <v>195</v>
       </c>
       <c r="D7" s="1">
-        <v>116550</v>
+        <v>143200</v>
       </c>
       <c r="E7" s="1">
-        <v>122300</v>
+        <v>150350</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3392,10 +3394,10 @@
         <v>193</v>
       </c>
       <c r="D8" s="1">
-        <v>184297</v>
+        <v>193500</v>
       </c>
       <c r="E8" s="1">
-        <v>204498</v>
+        <v>251300</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3409,10 +3411,10 @@
         <v>194</v>
       </c>
       <c r="D9" s="1">
-        <v>184297</v>
+        <v>193500</v>
       </c>
       <c r="E9" s="1">
-        <v>204498</v>
+        <v>251300</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3426,10 +3428,10 @@
         <v>195</v>
       </c>
       <c r="D10" s="1">
-        <v>194121</v>
+        <v>203850</v>
       </c>
       <c r="E10" s="1">
-        <v>208575</v>
+        <v>256250</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3443,7 +3445,7 @@
         <v>193</v>
       </c>
       <c r="F11" s="1">
-        <v>64350</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3457,7 +3459,7 @@
         <v>194</v>
       </c>
       <c r="F12" s="1">
-        <v>64350</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3471,7 +3473,7 @@
         <v>195</v>
       </c>
       <c r="F13" s="1">
-        <v>67260</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3485,7 +3487,7 @@
         <v>193</v>
       </c>
       <c r="F14" s="1">
-        <v>133075</v>
+        <v>163500</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3499,7 +3501,7 @@
         <v>194</v>
       </c>
       <c r="F15" s="1">
-        <v>133875</v>
+        <v>163500</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3513,7 +3515,7 @@
         <v>195</v>
       </c>
       <c r="F16" s="1">
-        <v>145763</v>
+        <v>176500</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3527,10 +3529,10 @@
         <v>193</v>
       </c>
       <c r="D17" s="1">
-        <v>174350</v>
+        <v>228900</v>
       </c>
       <c r="E17" s="1">
-        <v>174350</v>
+        <v>228900</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3544,10 +3546,10 @@
         <v>194</v>
       </c>
       <c r="D18" s="1">
-        <v>174350</v>
+        <v>228900</v>
       </c>
       <c r="E18" s="1">
-        <v>174350</v>
+        <v>228900</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3561,10 +3563,10 @@
         <v>195</v>
       </c>
       <c r="D19" s="1">
-        <v>186300</v>
+        <v>244500</v>
       </c>
       <c r="E19" s="1">
-        <v>186300</v>
+        <v>244500</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3578,10 +3580,10 @@
         <v>193</v>
       </c>
       <c r="D20" s="1">
-        <v>206731</v>
+        <v>271400</v>
       </c>
       <c r="E20" s="1">
-        <v>206731</v>
+        <v>271400</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3595,10 +3597,10 @@
         <v>194</v>
       </c>
       <c r="D21" s="1">
-        <v>206731</v>
+        <v>271400</v>
       </c>
       <c r="E21" s="1">
-        <v>206731</v>
+        <v>271400</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3612,10 +3614,10 @@
         <v>195</v>
       </c>
       <c r="D22" s="1">
-        <v>208285</v>
+        <v>273400</v>
       </c>
       <c r="E22" s="1">
-        <v>208285</v>
+        <v>273400</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3629,10 +3631,10 @@
         <v>193</v>
       </c>
       <c r="D23" s="1">
-        <v>271005</v>
+        <v>355700</v>
       </c>
       <c r="E23" s="1">
-        <v>271005</v>
+        <v>355700</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3646,10 +3648,10 @@
         <v>194</v>
       </c>
       <c r="D24" s="1">
-        <v>271005</v>
+        <v>355700</v>
       </c>
       <c r="E24" s="1">
-        <v>271005</v>
+        <v>355700</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3663,10 +3665,10 @@
         <v>195</v>
       </c>
       <c r="D25" s="1">
-        <v>286182</v>
+        <v>375600</v>
       </c>
       <c r="E25" s="1">
-        <v>286182</v>
+        <v>375600</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -6053,35 +6055,35 @@
         <v>56</v>
       </c>
       <c r="B55" s="2">
-        <f>B54*(1.05)</f>
+        <f t="shared" ref="B55:I55" si="0">B54*(1.05)</f>
         <v>306836.25</v>
       </c>
       <c r="C55" s="2">
-        <f>C54*(1.05)</f>
+        <f t="shared" si="0"/>
         <v>37687.65</v>
       </c>
       <c r="D55" s="2">
-        <f>D54*(1.05)</f>
+        <f t="shared" si="0"/>
         <v>71820</v>
       </c>
       <c r="E55" s="2">
-        <f>E54*(1.05)</f>
+        <f t="shared" si="0"/>
         <v>87088.05</v>
       </c>
       <c r="F55" s="2">
-        <f>F54*(1.05)</f>
+        <f t="shared" si="0"/>
         <v>100217.25</v>
       </c>
       <c r="G55" s="2">
-        <f>G54*(1.05)</f>
+        <f t="shared" si="0"/>
         <v>131964</v>
       </c>
       <c r="H55" s="2">
-        <f>H54*(1.05)</f>
+        <f t="shared" si="0"/>
         <v>413127.75</v>
       </c>
       <c r="I55" s="2">
-        <f>I54*(1.05)</f>
+        <f t="shared" si="0"/>
         <v>173365.5</v>
       </c>
     </row>
@@ -11220,10 +11222,10 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>25839</v>
+        <v>26974</v>
       </c>
       <c r="E2">
-        <v>28439</v>
+        <v>29689</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -11234,13 +11236,13 @@
         <v>105289</v>
       </c>
       <c r="C3">
-        <v>20196</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>24486</v>
+        <v>26974</v>
       </c>
       <c r="E3">
-        <v>26941</v>
+        <v>29689</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -11251,13 +11253,13 @@
         <v>140475</v>
       </c>
       <c r="C4">
-        <v>10098</v>
+        <v>10542</v>
       </c>
       <c r="D4">
-        <v>12243</v>
+        <v>12781</v>
       </c>
       <c r="E4">
-        <v>13471</v>
+        <v>14062</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -11268,13 +11270,13 @@
         <v>168040</v>
       </c>
       <c r="C5">
-        <v>10098</v>
+        <v>10542</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>13471</v>
+        <v>14062</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -11285,13 +11287,13 @@
         <v>157887</v>
       </c>
       <c r="C6">
-        <v>5643</v>
+        <v>5891</v>
       </c>
       <c r="D6">
-        <v>6798</v>
+        <v>7097</v>
       </c>
       <c r="E6">
-        <v>7484</v>
+        <v>7813</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -11302,13 +11304,13 @@
         <v>171861</v>
       </c>
       <c r="C7">
-        <v>5643</v>
+        <v>5891</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>7097</v>
       </c>
       <c r="E7">
-        <v>7484</v>
+        <v>7813</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939" firstSheet="8" activeTab="13"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939" firstSheet="8" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="281">
   <si>
     <t>MEDIDA</t>
   </si>
@@ -723,12 +723,6 @@
     <t>MOSQUITERO_FIJO</t>
   </si>
   <si>
-    <t>CAJON_BLOCK</t>
-  </si>
-  <si>
-    <t>CORTINAS</t>
-  </si>
-  <si>
     <t>PVC</t>
   </si>
   <si>
@@ -792,9 +786,6 @@
     <t>PUERTA_MOSQUITERO</t>
   </si>
   <si>
-    <t>6MM</t>
-  </si>
-  <si>
     <t>4+4</t>
   </si>
   <si>
@@ -835,14 +826,79 @@
   </si>
   <si>
     <t>GRANERO_ALUMINIO_SIN_HERRAJES</t>
+  </si>
+  <si>
+    <t>SUBITEM2</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CAJON_BLOCK_PRECIOS</t>
+  </si>
+  <si>
+    <t>CORTINAS_MODULO</t>
+  </si>
+  <si>
+    <t>LIVIANA_COMPLETA</t>
+  </si>
+  <si>
+    <t>LIVIANA_PANO_SOLO</t>
+  </si>
+  <si>
+    <t>REFORZADA_COMPLETA</t>
+  </si>
+  <si>
+    <t>REFORZADA_PANO_SOLO</t>
+  </si>
+  <si>
+    <t>SUPER_REFORZADA_COMPLETA</t>
+  </si>
+  <si>
+    <t>SUPER_REFORZADA_PANO_SOLO</t>
+  </si>
+  <si>
+    <t>BLANCO_COMPLETA</t>
+  </si>
+  <si>
+    <t>BLANCO_PANO_SOLO</t>
+  </si>
+  <si>
+    <t>SIMIL_MADERA_COMPLETA</t>
+  </si>
+  <si>
+    <t>SIMIL_MADERA_PANO_SOLO</t>
+  </si>
+  <si>
+    <t>BARRA_ANTIPANICO</t>
+  </si>
+  <si>
+    <t>LAMINADO</t>
+  </si>
+  <si>
+    <t>TEMPLADO</t>
+  </si>
+  <si>
+    <t>REFLECTIVO</t>
+  </si>
+  <si>
+    <t>LOW_E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -870,13 +926,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3278,7 +3340,7 @@
         <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3673,10 +3735,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>193</v>
@@ -3687,10 +3749,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>194</v>
@@ -3701,10 +3763,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>195</v>
@@ -3715,10 +3777,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>193</v>
@@ -3729,10 +3791,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>194</v>
@@ -3743,10 +3805,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>195</v>
@@ -3757,10 +3819,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>193</v>
@@ -3771,10 +3833,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>194</v>
@@ -3785,10 +3847,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>195</v>
@@ -3799,10 +3861,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>193</v>
@@ -3813,10 +3875,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>194</v>
@@ -3827,10 +3889,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>195</v>
@@ -3846,90 +3908,109 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>218</v>
       </c>
@@ -3939,11 +4020,11 @@
       <c r="C8" t="s">
         <v>220</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>10685</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>218</v>
       </c>
@@ -3953,33 +4034,33 @@
       <c r="C9" t="s">
         <v>221</v>
       </c>
-      <c r="D9">
-        <v>20505</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>18080</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>218</v>
       </c>
       <c r="B10" t="s">
         <v>222</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>7400</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>218</v>
       </c>
       <c r="B11" t="s">
         <v>223</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>4200</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>218</v>
       </c>
@@ -3989,11 +4070,11 @@
       <c r="C12" t="s">
         <v>220</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>13517</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>218</v>
       </c>
@@ -4003,422 +4084,647 @@
       <c r="C13" t="s">
         <v>221</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>20505</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>218</v>
       </c>
       <c r="B14" t="s">
         <v>225</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>5905</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
-      </c>
-      <c r="D15">
-        <v>48364</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+      <c r="E15">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>218</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="E16">
+        <v>48364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="C17" t="s">
-        <v>229</v>
-      </c>
-      <c r="D17">
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="E17">
+        <v>280585</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="C18" t="s">
         <v>190</v>
       </c>
-      <c r="D18">
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="E18">
+        <v>346865</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20">
+        <v>30208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" t="s">
+        <v>267</v>
+      </c>
+      <c r="E21">
+        <v>23180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" t="s">
+        <v>265</v>
+      </c>
+      <c r="C22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D22" t="s">
+        <v>268</v>
+      </c>
+      <c r="E22">
+        <v>37410</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B23" t="s">
+        <v>265</v>
+      </c>
+      <c r="C23" t="s">
+        <v>227</v>
+      </c>
+      <c r="D23" t="s">
+        <v>269</v>
+      </c>
+      <c r="E23">
+        <v>28263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" t="s">
+        <v>265</v>
+      </c>
+      <c r="C24" t="s">
+        <v>227</v>
+      </c>
+      <c r="D24" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24">
+        <v>52671</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>218</v>
+      </c>
+      <c r="B25" t="s">
+        <v>265</v>
+      </c>
+      <c r="C25" t="s">
+        <v>227</v>
+      </c>
+      <c r="D25" t="s">
+        <v>271</v>
+      </c>
+      <c r="E25">
+        <v>39099</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>218</v>
+      </c>
+      <c r="B27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C27" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" t="s">
+        <v>272</v>
+      </c>
+      <c r="E27">
+        <v>188750</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>218</v>
+      </c>
+      <c r="B28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" t="s">
+        <v>273</v>
+      </c>
+      <c r="E28">
+        <v>139851</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>218</v>
+      </c>
+      <c r="B29" t="s">
+        <v>265</v>
+      </c>
+      <c r="C29" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" t="s">
+        <v>274</v>
+      </c>
+      <c r="E29">
+        <v>204007</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>218</v>
+      </c>
+      <c r="B30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" t="s">
+        <v>275</v>
+      </c>
+      <c r="E30">
+        <v>155108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>228</v>
+      </c>
+      <c r="B31" t="s">
+        <v>229</v>
+      </c>
+      <c r="E31">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" t="s">
         <v>230</v>
       </c>
-      <c r="B19" t="s">
+      <c r="E32">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>228</v>
+      </c>
+      <c r="B33" t="s">
         <v>231</v>
       </c>
-      <c r="D19">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>230</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="E33">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>228</v>
+      </c>
+      <c r="B34" t="s">
         <v>232</v>
       </c>
-      <c r="D20">
+      <c r="E34">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>228</v>
+      </c>
+      <c r="B36" t="s">
+        <v>234</v>
+      </c>
+      <c r="E36">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>228</v>
+      </c>
+      <c r="B37" t="s">
+        <v>235</v>
+      </c>
+      <c r="E37">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E38">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" t="s">
+        <v>238</v>
+      </c>
+      <c r="E39">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>239</v>
+      </c>
+      <c r="B41" t="s">
+        <v>240</v>
+      </c>
+      <c r="E41">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>239</v>
+      </c>
+      <c r="B42" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" t="s">
+        <v>242</v>
+      </c>
+      <c r="E43">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>239</v>
+      </c>
+      <c r="B44" t="s">
+        <v>243</v>
+      </c>
+      <c r="E44">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>239</v>
+      </c>
+      <c r="B45" t="s">
+        <v>276</v>
+      </c>
+      <c r="E45">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>239</v>
+      </c>
+      <c r="B46" t="s">
+        <v>244</v>
+      </c>
+      <c r="C46" t="s">
+        <v>220</v>
+      </c>
+      <c r="E46">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>239</v>
+      </c>
+      <c r="B47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C47" t="s">
+        <v>221</v>
+      </c>
+      <c r="E47">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>239</v>
+      </c>
+      <c r="B48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E48">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>239</v>
+      </c>
+      <c r="B49" t="s">
+        <v>246</v>
+      </c>
+      <c r="C49" t="s">
+        <v>220</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>239</v>
+      </c>
+      <c r="B50" t="s">
+        <v>246</v>
+      </c>
+      <c r="C50" t="s">
+        <v>221</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>247</v>
+      </c>
+      <c r="B51">
+        <v>80</v>
+      </c>
+      <c r="E51">
+        <v>101970</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>247</v>
+      </c>
+      <c r="B52">
+        <v>90</v>
+      </c>
+      <c r="E52">
+        <v>112167</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53">
+        <v>29500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="E54">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>5</v>
+      </c>
+      <c r="E55">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>6</v>
+      </c>
+      <c r="E56">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
+      </c>
+      <c r="E57">
         <v>45000</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" t="s">
-        <v>233</v>
-      </c>
-      <c r="D21">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>230</v>
-      </c>
-      <c r="B22" t="s">
-        <v>234</v>
-      </c>
-      <c r="D22">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>230</v>
-      </c>
-      <c r="B23" t="s">
-        <v>235</v>
-      </c>
-      <c r="D23">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>230</v>
-      </c>
-      <c r="B24" t="s">
-        <v>236</v>
-      </c>
-      <c r="D24">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>230</v>
-      </c>
-      <c r="B25" t="s">
-        <v>237</v>
-      </c>
-      <c r="D25">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>238</v>
-      </c>
-      <c r="B26" t="s">
-        <v>239</v>
-      </c>
-      <c r="D26">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>238</v>
-      </c>
-      <c r="B27" t="s">
-        <v>240</v>
-      </c>
-      <c r="D27">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>241</v>
-      </c>
-      <c r="B28" t="s">
-        <v>153</v>
-      </c>
-      <c r="D28">
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>241</v>
-      </c>
-      <c r="B29" t="s">
-        <v>242</v>
-      </c>
-      <c r="D29">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>241</v>
-      </c>
-      <c r="B30" t="s">
-        <v>243</v>
-      </c>
-      <c r="D30">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>241</v>
-      </c>
-      <c r="B31" t="s">
-        <v>244</v>
-      </c>
-      <c r="D31">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>241</v>
-      </c>
-      <c r="B32" t="s">
-        <v>245</v>
-      </c>
-      <c r="D32">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>241</v>
-      </c>
-      <c r="B33" t="s">
-        <v>246</v>
-      </c>
-      <c r="C33" t="s">
-        <v>220</v>
-      </c>
-      <c r="D33">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>241</v>
-      </c>
-      <c r="B34" t="s">
-        <v>246</v>
-      </c>
-      <c r="C34" t="s">
-        <v>221</v>
-      </c>
-      <c r="D34">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>241</v>
-      </c>
-      <c r="B35" t="s">
-        <v>247</v>
-      </c>
-      <c r="D35">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>241</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>10</v>
+      </c>
+      <c r="E58">
+        <v>67000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" t="s">
         <v>248</v>
       </c>
-      <c r="C36" t="s">
-        <v>220</v>
-      </c>
-      <c r="D36">
+      <c r="E59">
+        <v>59000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" t="s">
+        <v>249</v>
+      </c>
+      <c r="E60">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" t="s">
+        <v>61</v>
+      </c>
+      <c r="E61">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>241</v>
-      </c>
-      <c r="B37" t="s">
-        <v>248</v>
-      </c>
-      <c r="C37" t="s">
-        <v>221</v>
-      </c>
-      <c r="D37">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" t="s">
+        <v>277</v>
+      </c>
+      <c r="E62">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>249</v>
-      </c>
-      <c r="B38">
-        <v>80</v>
-      </c>
-      <c r="D38">
-        <v>101970</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>249</v>
-      </c>
-      <c r="B39">
-        <v>90</v>
-      </c>
-      <c r="D39">
-        <v>112167</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>4</v>
       </c>
-      <c r="B40" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40">
-        <v>16459</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B63" t="s">
+        <v>278</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>4</v>
       </c>
-      <c r="B41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41">
-        <v>21250</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B64" t="s">
+        <v>62</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>4</v>
       </c>
-      <c r="B42" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42">
-        <v>27169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B65" t="s">
+        <v>279</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>4</v>
       </c>
-      <c r="B43" t="s">
-        <v>250</v>
-      </c>
-      <c r="D43">
-        <v>33410</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
-      <c r="D44">
-        <v>27012</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45">
-        <v>60797</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46">
-        <v>65546</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" t="s">
-        <v>251</v>
-      </c>
-      <c r="D47">
-        <v>73221</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" t="s">
-        <v>252</v>
-      </c>
-      <c r="D48">
-        <v>88575</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49">
-        <v>12600</v>
+      <c r="B66" t="s">
+        <v>280</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4433,7 +4739,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B1" t="s">
         <v>205</v>
@@ -4444,12 +4750,12 @@
         <v>215</v>
       </c>
       <c r="B2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4457,18 +4763,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sebamarcotizador\backend\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\German\Documents\sebamarapp\backend\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243BC3EC-D48F-4816-B0D0-782664B379D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939" firstSheet="8" activeTab="12"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="939" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>
@@ -27,10 +28,19 @@
     <sheet name="SUPERFICIES" sheetId="13" r:id="rId13"/>
     <sheet name="COLORES" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -888,7 +898,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1219,14 +1229,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1243,7 +1253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1260,7 +1270,7 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1277,7 +1287,7 @@
         <v>3784</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1294,7 +1304,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1311,7 +1321,7 @@
         <v>5959</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1328,7 +1338,7 @@
         <v>7568</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1345,7 +1355,7 @@
         <v>9197</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1362,7 +1372,7 @@
         <v>10278</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1379,7 +1389,7 @@
         <v>4509</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1396,7 +1406,7 @@
         <v>6309</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1413,7 +1423,7 @@
         <v>8115</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1430,7 +1440,7 @@
         <v>9915</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1447,7 +1457,7 @@
         <v>12625</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1464,7 +1474,7 @@
         <v>15328</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1481,7 +1491,7 @@
         <v>17127</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1498,7 +1508,7 @@
         <v>11359</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1515,7 +1525,7 @@
         <v>13884</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1532,7 +1542,7 @@
         <v>17668</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1549,7 +1559,7 @@
         <v>21459</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1566,7 +1576,7 @@
         <v>23977</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -1583,7 +1593,7 @@
         <v>14603</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1600,7 +1610,7 @@
         <v>17853</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -1617,7 +1627,7 @@
         <v>22718</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1634,7 +1644,7 @@
         <v>27583</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1651,7 +1661,7 @@
         <v>30833</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1668,7 +1678,7 @@
         <v>34077</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -1685,7 +1695,7 @@
         <v>37320</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -1702,7 +1712,7 @@
         <v>16231</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -1719,7 +1729,7 @@
         <v>19830</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -1736,7 +1746,7 @@
         <v>25243</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1753,7 +1763,7 @@
         <v>30655</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>163</v>
       </c>
@@ -1770,7 +1780,7 @@
         <v>37861</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>164</v>
       </c>
@@ -1787,7 +1797,7 @@
         <v>41467</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -1804,7 +1814,7 @@
         <v>17853</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -1821,7 +1831,7 @@
         <v>21815</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -1838,7 +1848,7 @@
         <v>27768</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -1855,7 +1865,7 @@
         <v>33714</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -1872,7 +1882,7 @@
         <v>37683</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -1889,7 +1899,7 @@
         <v>41652</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -1906,7 +1916,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -1923,7 +1933,7 @@
         <v>22718</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -1940,7 +1950,7 @@
         <v>27768</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -1957,7 +1967,7 @@
         <v>35336</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -1974,7 +1984,7 @@
         <v>42911</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -1991,7 +2001,7 @@
         <v>47961</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -2008,7 +2018,7 @@
         <v>53004</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -2025,7 +2035,7 @@
         <v>58060</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -2042,7 +2052,7 @@
         <v>30833</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
@@ -2059,7 +2069,7 @@
         <v>37683</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -2076,7 +2086,7 @@
         <v>50486</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -2093,7 +2103,7 @@
         <v>61304</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -2110,7 +2120,7 @@
         <v>68516</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
@@ -2127,7 +2137,7 @@
         <v>75729</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -2144,7 +2154,7 @@
         <v>82941</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -2171,11 +2181,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>165</v>
       </c>
@@ -2195,7 +2205,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>168</v>
       </c>
@@ -2215,7 +2225,7 @@
         <v>61992</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>168</v>
       </c>
@@ -2235,7 +2245,7 @@
         <v>69741</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>168</v>
       </c>
@@ -2255,7 +2265,7 @@
         <v>77490</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -2275,7 +2285,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>168</v>
       </c>
@@ -2295,7 +2305,7 @@
         <v>67158</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>168</v>
       </c>
@@ -2315,7 +2325,7 @@
         <v>72324</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>168</v>
       </c>
@@ -2335,7 +2345,7 @@
         <v>80073</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>168</v>
       </c>
@@ -2355,7 +2365,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>168</v>
       </c>
@@ -2375,7 +2385,7 @@
         <v>92988</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>168</v>
       </c>
@@ -2395,7 +2405,7 @@
         <v>77490</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>168</v>
       </c>
@@ -2415,7 +2425,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>168</v>
       </c>
@@ -2435,7 +2445,7 @@
         <v>90405</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -2455,7 +2465,7 @@
         <v>98154</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>168</v>
       </c>
@@ -2475,7 +2485,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>168</v>
       </c>
@@ -2495,7 +2505,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>168</v>
       </c>
@@ -2515,7 +2525,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>168</v>
       </c>
@@ -2535,7 +2545,7 @@
         <v>95571</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -2555,7 +2565,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -2575,7 +2585,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>168</v>
       </c>
@@ -2595,7 +2605,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>168</v>
       </c>
@@ -2615,7 +2625,7 @@
         <v>92988</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -2635,7 +2645,7 @@
         <v>100737</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>168</v>
       </c>
@@ -2655,7 +2665,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>168</v>
       </c>
@@ -2675,7 +2685,7 @@
         <v>113652</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>168</v>
       </c>
@@ -2695,7 +2705,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>168</v>
       </c>
@@ -2715,7 +2725,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>168</v>
       </c>
@@ -2735,7 +2745,7 @@
         <v>116235</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>168</v>
       </c>
@@ -2755,7 +2765,7 @@
         <v>123984</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>168</v>
       </c>
@@ -2775,7 +2785,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>169</v>
       </c>
@@ -2795,7 +2805,7 @@
         <v>98154</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>169</v>
       </c>
@@ -2815,7 +2825,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>169</v>
       </c>
@@ -2835,7 +2845,7 @@
         <v>136899</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>169</v>
       </c>
@@ -2861,11 +2871,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2873,7 +2883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -2881,7 +2891,7 @@
         <v>11094</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -2889,7 +2899,7 @@
         <v>12830</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -2897,7 +2907,7 @@
         <v>14565</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -2905,7 +2915,7 @@
         <v>16300</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>171</v>
       </c>
@@ -2913,7 +2923,7 @@
         <v>18905</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>172</v>
       </c>
@@ -2921,7 +2931,7 @@
         <v>21508</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>173</v>
       </c>
@@ -2929,7 +2939,7 @@
         <v>23244</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -2937,7 +2947,7 @@
         <v>17580</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2945,7 +2955,7 @@
         <v>19772</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2953,7 +2963,7 @@
         <v>21965</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2961,7 +2971,7 @@
         <v>25254</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -2969,7 +2979,7 @@
         <v>28542</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2977,7 +2987,7 @@
         <v>30736</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>174</v>
       </c>
@@ -2985,7 +2995,7 @@
         <v>32927</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>175</v>
       </c>
@@ -2993,7 +3003,7 @@
         <v>35120</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -3001,7 +3011,7 @@
         <v>21508</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>156</v>
       </c>
@@ -3009,7 +3019,7 @@
         <v>23853</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>157</v>
       </c>
@@ -3017,7 +3027,7 @@
         <v>27371</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>158</v>
       </c>
@@ -3025,7 +3035,7 @@
         <v>30887</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>159</v>
       </c>
@@ -3033,7 +3043,7 @@
         <v>33232</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>160</v>
       </c>
@@ -3041,7 +3051,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>161</v>
       </c>
@@ -3049,7 +3059,7 @@
         <v>37923</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3057,7 +3067,7 @@
         <v>24980</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3065,7 +3075,7 @@
         <v>27630</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3073,7 +3083,7 @@
         <v>31603</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -3081,7 +3091,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>162</v>
       </c>
@@ -3089,7 +3099,7 @@
         <v>38227</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>163</v>
       </c>
@@ -3097,7 +3107,7 @@
         <v>40877</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>164</v>
       </c>
@@ -3105,7 +3115,7 @@
         <v>43526</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>176</v>
       </c>
@@ -3113,7 +3123,7 @@
         <v>31405</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -3121,7 +3131,7 @@
         <v>35836</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>178</v>
       </c>
@@ -3129,7 +3139,7 @@
         <v>40268</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -3137,7 +3147,7 @@
         <v>43221</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>180</v>
       </c>
@@ -3145,7 +3155,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>181</v>
       </c>
@@ -3153,7 +3163,7 @@
         <v>49130</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -3161,7 +3171,7 @@
         <v>32982</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -3169,7 +3179,7 @@
         <v>37565</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -3177,7 +3187,7 @@
         <v>42148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -3185,7 +3195,7 @@
         <v>45203</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -3193,7 +3203,7 @@
         <v>48257</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -3201,7 +3211,7 @@
         <v>51313</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -3209,7 +3219,7 @@
         <v>38292</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>183</v>
       </c>
@@ -3217,7 +3227,7 @@
         <v>43518</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>184</v>
       </c>
@@ -3225,7 +3235,7 @@
         <v>48743</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>185</v>
       </c>
@@ -3233,7 +3243,7 @@
         <v>52226</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>186</v>
       </c>
@@ -3241,7 +3251,7 @@
         <v>55709</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>187</v>
       </c>
@@ -3249,7 +3259,7 @@
         <v>59193</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -3257,7 +3267,7 @@
         <v>41832</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -3265,7 +3275,7 @@
         <v>47486</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -3273,7 +3283,7 @@
         <v>53139</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -3281,7 +3291,7 @@
         <v>56908</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -3289,7 +3299,7 @@
         <v>60677</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -3297,7 +3307,7 @@
         <v>64446</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -3311,16 +3321,16 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="11.3984375" style="1"/>
     <col min="2" max="2" width="21" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="1"/>
+    <col min="3" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
@@ -3343,7 +3353,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>191</v>
       </c>
@@ -3360,7 +3370,7 @@
         <v>81100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>191</v>
       </c>
@@ -3377,7 +3387,7 @@
         <v>81100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>191</v>
       </c>
@@ -3394,7 +3404,7 @@
         <v>86112</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>191</v>
       </c>
@@ -3411,7 +3421,7 @@
         <v>144100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>191</v>
       </c>
@@ -3428,7 +3438,7 @@
         <v>144100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>191</v>
       </c>
@@ -3445,7 +3455,7 @@
         <v>150350</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>191</v>
       </c>
@@ -3462,7 +3472,7 @@
         <v>251300</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>191</v>
       </c>
@@ -3479,7 +3489,7 @@
         <v>251300</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>191</v>
       </c>
@@ -3496,7 +3506,7 @@
         <v>256250</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>191</v>
       </c>
@@ -3510,7 +3520,7 @@
         <v>79500</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>191</v>
       </c>
@@ -3524,7 +3534,7 @@
         <v>79500</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>191</v>
       </c>
@@ -3538,7 +3548,7 @@
         <v>82600</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>191</v>
       </c>
@@ -3552,7 +3562,7 @@
         <v>163500</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>191</v>
       </c>
@@ -3566,7 +3576,7 @@
         <v>163500</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>191</v>
       </c>
@@ -3580,7 +3590,7 @@
         <v>176500</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>200</v>
       </c>
@@ -3597,7 +3607,7 @@
         <v>228900</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>200</v>
       </c>
@@ -3614,7 +3624,7 @@
         <v>228900</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>200</v>
       </c>
@@ -3631,7 +3641,7 @@
         <v>244500</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>200</v>
       </c>
@@ -3648,7 +3658,7 @@
         <v>271400</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>200</v>
       </c>
@@ -3665,7 +3675,7 @@
         <v>271400</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>200</v>
       </c>
@@ -3682,7 +3692,7 @@
         <v>273400</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>200</v>
       </c>
@@ -3699,7 +3709,7 @@
         <v>355700</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>200</v>
       </c>
@@ -3716,7 +3726,7 @@
         <v>355700</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>200</v>
       </c>
@@ -3733,7 +3743,7 @@
         <v>375600</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>257</v>
       </c>
@@ -3747,7 +3757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>257</v>
       </c>
@@ -3761,7 +3771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>257</v>
       </c>
@@ -3775,7 +3785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>257</v>
       </c>
@@ -3789,7 +3799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>257</v>
       </c>
@@ -3803,7 +3813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>257</v>
       </c>
@@ -3817,7 +3827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>257</v>
       </c>
@@ -3831,7 +3841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>257</v>
       </c>
@@ -3845,7 +3855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>257</v>
       </c>
@@ -3859,7 +3869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>257</v>
       </c>
@@ -3873,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>257</v>
       </c>
@@ -3887,7 +3897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>257</v>
       </c>
@@ -3907,15 +3917,15 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.3984375" customWidth="1"/>
+    <col min="3" max="3" width="20.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>202</v>
       </c>
@@ -3932,7 +3942,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>206</v>
       </c>
@@ -3945,7 +3955,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>206</v>
       </c>
@@ -3958,7 +3968,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
         <v>206</v>
       </c>
@@ -3971,7 +3981,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>206</v>
       </c>
@@ -3984,7 +3994,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>206</v>
       </c>
@@ -3997,7 +4007,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>206</v>
       </c>
@@ -4010,7 +4020,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>218</v>
       </c>
@@ -4024,7 +4034,7 @@
         <v>10685</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>218</v>
       </c>
@@ -4038,7 +4048,7 @@
         <v>18080</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>218</v>
       </c>
@@ -4049,7 +4059,7 @@
         <v>7400</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>218</v>
       </c>
@@ -4060,7 +4070,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>218</v>
       </c>
@@ -4074,7 +4084,7 @@
         <v>13517</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>218</v>
       </c>
@@ -4088,7 +4098,7 @@
         <v>20505</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>218</v>
       </c>
@@ -4099,7 +4109,7 @@
         <v>5905</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>218</v>
       </c>
@@ -4110,7 +4120,7 @@
         <v>18500</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>218</v>
       </c>
@@ -4121,7 +4131,7 @@
         <v>48364</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>218</v>
       </c>
@@ -4135,7 +4145,7 @@
         <v>280585</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>218</v>
       </c>
@@ -4149,7 +4159,7 @@
         <v>346865</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>218</v>
       </c>
@@ -4166,7 +4176,7 @@
         <v>30208</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>218</v>
       </c>
@@ -4183,7 +4193,7 @@
         <v>23180</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>218</v>
       </c>
@@ -4200,7 +4210,7 @@
         <v>37410</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>218</v>
       </c>
@@ -4217,7 +4227,7 @@
         <v>28263</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>218</v>
       </c>
@@ -4234,7 +4244,7 @@
         <v>52671</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>218</v>
       </c>
@@ -4251,7 +4261,7 @@
         <v>39099</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>218</v>
       </c>
@@ -4268,7 +4278,7 @@
         <v>188750</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>218</v>
       </c>
@@ -4285,7 +4295,7 @@
         <v>139851</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>218</v>
       </c>
@@ -4302,7 +4312,7 @@
         <v>204007</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>218</v>
       </c>
@@ -4319,7 +4329,7 @@
         <v>155108</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>228</v>
       </c>
@@ -4330,7 +4340,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>228</v>
       </c>
@@ -4341,7 +4351,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>228</v>
       </c>
@@ -4352,7 +4362,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>228</v>
       </c>
@@ -4363,7 +4373,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>228</v>
       </c>
@@ -4374,7 +4384,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>228</v>
       </c>
@@ -4385,7 +4395,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>228</v>
       </c>
@@ -4396,7 +4406,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>236</v>
       </c>
@@ -4407,7 +4417,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>236</v>
       </c>
@@ -4418,7 +4428,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>239</v>
       </c>
@@ -4429,7 +4439,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>239</v>
       </c>
@@ -4440,7 +4450,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>239</v>
       </c>
@@ -4451,7 +4461,7 @@
         <v>850000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>239</v>
       </c>
@@ -4462,7 +4472,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>239</v>
       </c>
@@ -4473,7 +4483,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>239</v>
       </c>
@@ -4484,7 +4494,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>239</v>
       </c>
@@ -4498,7 +4508,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>239</v>
       </c>
@@ -4512,7 +4522,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>239</v>
       </c>
@@ -4523,7 +4533,7 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>239</v>
       </c>
@@ -4537,7 +4547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>239</v>
       </c>
@@ -4551,7 +4561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>247</v>
       </c>
@@ -4562,7 +4572,7 @@
         <v>101970</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>247</v>
       </c>
@@ -4573,7 +4583,7 @@
         <v>112167</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -4584,7 +4594,7 @@
         <v>29500</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -4595,7 +4605,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -4606,7 +4616,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -4617,7 +4627,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -4628,7 +4638,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -4639,7 +4649,7 @@
         <v>67000</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -4650,7 +4660,7 @@
         <v>59000</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -4661,7 +4671,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -4672,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -4683,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -4694,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -4705,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -4716,7 +4726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -4733,11 +4743,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>250</v>
       </c>
@@ -4745,7 +4755,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>215</v>
       </c>
@@ -4753,7 +4763,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>252</v>
       </c>
@@ -4761,7 +4771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>253</v>
       </c>
@@ -4769,7 +4779,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>255</v>
       </c>
@@ -4783,14 +4793,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4819,7 +4829,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4848,7 +4858,7 @@
         <v>36118</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -4877,7 +4887,7 @@
         <v>41278</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -4906,7 +4916,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -4935,7 +4945,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -4964,7 +4974,7 @@
         <v>59337</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -4993,7 +5003,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -5022,7 +5032,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -5051,7 +5061,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -5080,7 +5090,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -5109,7 +5119,7 @@
         <v>56757</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -5138,7 +5148,7 @@
         <v>61916</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -5167,7 +5177,7 @@
         <v>69656</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -5196,7 +5206,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -5225,7 +5235,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -5254,7 +5264,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -5283,7 +5293,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -5312,7 +5322,7 @@
         <v>79975</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -5341,7 +5351,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -5370,7 +5380,7 @@
         <v>92875</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -5399,7 +5409,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -5428,7 +5438,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -5457,7 +5467,7 @@
         <v>90295</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -5486,7 +5496,7 @@
         <v>98034</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -5515,7 +5525,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -5544,7 +5554,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -5573,7 +5583,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -5602,7 +5612,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -5631,7 +5641,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -5660,7 +5670,7 @@
         <v>95454</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -5689,7 +5699,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>163</v>
       </c>
@@ -5718,7 +5728,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>164</v>
       </c>
@@ -5747,7 +5757,7 @@
         <v>118673</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -5776,7 +5786,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -5805,7 +5815,7 @@
         <v>92875</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -5834,7 +5844,7 @@
         <v>100614</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -5863,7 +5873,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -5892,7 +5902,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -5921,7 +5931,7 @@
         <v>118673</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -5950,7 +5960,7 @@
         <v>123833</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -5979,7 +5989,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -6008,7 +6018,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -6037,7 +6047,7 @@
         <v>116093</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -6066,7 +6076,7 @@
         <v>123833</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -6095,7 +6105,7 @@
         <v>128993</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -6124,7 +6134,7 @@
         <v>134152</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -6153,7 +6163,7 @@
         <v>139312</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -6182,7 +6192,7 @@
         <v>128993</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
@@ -6211,7 +6221,7 @@
         <v>134152</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -6240,7 +6250,7 @@
         <v>141892</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -6269,7 +6279,7 @@
         <v>149631</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -6298,7 +6308,7 @@
         <v>154791</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
@@ -6327,7 +6337,7 @@
         <v>159951</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -6356,7 +6366,7 @@
         <v>165110</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -6400,11 +6410,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6430,7 +6440,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -6456,7 +6466,7 @@
         <v>13413</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -6482,7 +6492,7 @@
         <v>17896</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -6508,7 +6518,7 @@
         <v>22380</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -6534,7 +6544,7 @@
         <v>26863</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6560,7 +6570,7 @@
         <v>31346</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -6586,7 +6596,7 @@
         <v>35830</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6612,7 +6622,7 @@
         <v>40313</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -6638,7 +6648,7 @@
         <v>17896</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -6664,7 +6674,7 @@
         <v>23858</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -6690,7 +6700,7 @@
         <v>29819</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -6716,7 +6726,7 @@
         <v>35781</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -6742,7 +6752,7 @@
         <v>41742</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -6768,7 +6778,7 @@
         <v>47703</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -6794,7 +6804,7 @@
         <v>53665</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -6820,7 +6830,7 @@
         <v>22380</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -6846,7 +6856,7 @@
         <v>29819</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -6872,7 +6882,7 @@
         <v>37259</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -6898,7 +6908,7 @@
         <v>44698</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -6924,7 +6934,7 @@
         <v>52138</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -6950,7 +6960,7 @@
         <v>59577</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -6976,7 +6986,7 @@
         <v>67017</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -7002,7 +7012,7 @@
         <v>26863</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -7028,7 +7038,7 @@
         <v>35781</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -7054,7 +7064,7 @@
         <v>44698</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -7080,7 +7090,7 @@
         <v>53616</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -7106,7 +7116,7 @@
         <v>62534</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -7132,7 +7142,7 @@
         <v>71451</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -7158,7 +7168,7 @@
         <v>80369</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -7184,7 +7194,7 @@
         <v>31346</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -7210,7 +7220,7 @@
         <v>41742</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -7236,7 +7246,7 @@
         <v>62534</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -7262,7 +7272,7 @@
         <v>72930</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -7288,7 +7298,7 @@
         <v>83325</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -7314,7 +7324,7 @@
         <v>93721</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -7340,7 +7350,7 @@
         <v>35830</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -7366,7 +7376,7 @@
         <v>47703</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -7392,7 +7402,7 @@
         <v>59577</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -7418,7 +7428,7 @@
         <v>71451</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -7444,7 +7454,7 @@
         <v>83325</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -7470,7 +7480,7 @@
         <v>95199</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -7496,7 +7506,7 @@
         <v>107073</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -7522,7 +7532,7 @@
         <v>40313</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -7548,7 +7558,7 @@
         <v>53665</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -7574,7 +7584,7 @@
         <v>67017</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -7600,7 +7610,7 @@
         <v>80369</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -7626,7 +7636,7 @@
         <v>93721</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -7652,7 +7662,7 @@
         <v>107073</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -7678,7 +7688,7 @@
         <v>120425</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -7704,7 +7714,7 @@
         <v>44723</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -7730,7 +7740,7 @@
         <v>59639</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -7756,7 +7766,7 @@
         <v>74554</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -7782,7 +7792,7 @@
         <v>89470</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -7808,7 +7818,7 @@
         <v>104386</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -7834,7 +7844,7 @@
         <v>119301</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -7860,7 +7870,7 @@
         <v>134217</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -7886,7 +7896,7 @@
         <v>49194</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -7912,7 +7922,7 @@
         <v>65600</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -7938,7 +7948,7 @@
         <v>82006</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -7964,7 +7974,7 @@
         <v>98412</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -7990,7 +8000,7 @@
         <v>114818</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -8016,7 +8026,7 @@
         <v>131224</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>35</v>
       </c>
@@ -8042,7 +8052,7 @@
         <v>147630</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -8068,7 +8078,7 @@
         <v>62619</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -8094,7 +8104,7 @@
         <v>83484</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -8120,7 +8130,7 @@
         <v>104349</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -8146,7 +8156,7 @@
         <v>125214</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -8172,7 +8182,7 @@
         <v>138383</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -8198,7 +8208,7 @@
         <v>151552</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -8230,11 +8240,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8263,7 +8273,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -8292,7 +8302,7 @@
         <v>24806</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -8321,7 +8331,7 @@
         <v>27907</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -8350,7 +8360,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -8379,7 +8389,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -8408,7 +8418,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -8437,7 +8447,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -8466,7 +8476,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -8495,7 +8505,7 @@
         <v>27907</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -8524,7 +8534,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -8553,7 +8563,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -8582,7 +8592,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -8611,7 +8621,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -8640,7 +8650,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -8669,7 +8679,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -8698,7 +8708,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -8727,7 +8737,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -8756,7 +8766,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -8785,7 +8795,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -8814,7 +8824,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -8843,7 +8853,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -8872,7 +8882,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -8901,7 +8911,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -8930,7 +8940,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -8959,7 +8969,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -8988,7 +8998,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -9017,7 +9027,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -9046,7 +9056,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -9075,7 +9085,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -9104,7 +9114,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -9133,7 +9143,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -9162,7 +9172,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -9191,7 +9201,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -9220,7 +9230,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -9249,7 +9259,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -9278,7 +9288,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -9307,7 +9317,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -9336,7 +9346,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -9365,7 +9375,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -9394,7 +9404,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -9423,7 +9433,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -9452,7 +9462,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -9481,7 +9491,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -9510,7 +9520,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -9539,7 +9549,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -9568,7 +9578,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -9597,7 +9607,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -9626,7 +9636,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -9655,7 +9665,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -9684,7 +9694,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -9713,7 +9723,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -9742,7 +9752,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -9771,7 +9781,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -9800,7 +9810,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -9829,7 +9839,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -9858,7 +9868,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -9887,7 +9897,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -9916,7 +9926,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -9945,7 +9955,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -9974,7 +9984,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -10003,7 +10013,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -10032,7 +10042,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>35</v>
       </c>
@@ -10061,7 +10071,7 @@
         <v>68218</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -10090,7 +10100,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -10119,7 +10129,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -10148,7 +10158,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -10177,7 +10187,7 @@
         <v>68218</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -10206,7 +10216,7 @@
         <v>71318</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -10235,7 +10245,7 @@
         <v>74419</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -10270,11 +10280,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -10300,7 +10310,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -10326,7 +10336,7 @@
         <v>115033</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -10352,7 +10362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -10378,7 +10388,7 @@
         <v>83034</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -10404,7 +10414,7 @@
         <v>41517</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -10430,7 +10440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -10456,7 +10466,7 @@
         <v>23064</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -10482,7 +10492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -10508,7 +10518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -10534,7 +10544,7 @@
         <v>41517</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -10560,7 +10570,7 @@
         <v>23064</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -10586,7 +10596,7 @@
         <v>92257</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -10612,7 +10622,7 @@
         <v>29219</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -10638,7 +10648,7 @@
         <v>18446</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -10664,7 +10674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -10690,7 +10700,7 @@
         <v>69199</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -10716,7 +10726,7 @@
         <v>69199</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>141</v>
       </c>
@@ -10742,7 +10752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>142</v>
       </c>
@@ -10774,11 +10784,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -10798,7 +10808,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>143</v>
       </c>
@@ -10818,7 +10828,7 @@
         <v>51329</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -10838,7 +10848,7 @@
         <v>51329</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -10858,7 +10868,7 @@
         <v>40524</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -10878,7 +10888,7 @@
         <v>40524</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>147</v>
       </c>
@@ -10898,7 +10908,7 @@
         <v>27014</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -10918,7 +10928,7 @@
         <v>27014</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -10938,7 +10948,7 @@
         <v>67537</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -10964,11 +10974,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -10997,7 +11007,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -11026,7 +11036,7 @@
         <v>70560</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -11055,7 +11065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -11084,7 +11094,7 @@
         <v>90720</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -11113,7 +11123,7 @@
         <v>45360</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -11142,7 +11152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -11171,7 +11181,7 @@
         <v>32760</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -11200,7 +11210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -11229,7 +11239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -11258,7 +11268,7 @@
         <v>95760</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -11287,7 +11297,7 @@
         <v>57960</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -11316,7 +11326,7 @@
         <v>131040</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -11345,7 +11355,7 @@
         <v>59220</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -11374,7 +11384,7 @@
         <v>34020</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -11403,7 +11413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -11432,7 +11442,7 @@
         <v>133560</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -11461,7 +11471,7 @@
         <v>57960</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -11496,11 +11506,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -11517,7 +11527,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -11534,7 +11544,7 @@
         <v>29689</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -11551,7 +11561,7 @@
         <v>29689</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -11568,7 +11578,7 @@
         <v>14062</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>152</v>
       </c>
@@ -11585,7 +11595,7 @@
         <v>14062</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -11602,7 +11612,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -11619,7 +11629,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -11642,14 +11652,14 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11663,7 +11673,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -11677,7 +11687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -11691,7 +11701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -11705,7 +11715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -11719,7 +11729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -11733,7 +11743,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>97</v>
       </c>
@@ -11747,7 +11757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>156</v>
       </c>
@@ -11761,7 +11771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>157</v>
       </c>
@@ -11775,7 +11785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>158</v>
       </c>
@@ -11789,7 +11799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>159</v>
       </c>
@@ -11803,7 +11813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>160</v>
       </c>
@@ -11817,7 +11827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>161</v>
       </c>
@@ -11831,7 +11841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -11845,7 +11855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -11859,7 +11869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -11873,7 +11883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -11887,7 +11897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
@@ -11901,7 +11911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -11915,7 +11925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -11929,7 +11939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -11943,7 +11953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -11957,7 +11967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -11971,7 +11981,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -11985,7 +11995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>162</v>
       </c>
@@ -11999,7 +12009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>163</v>
       </c>
@@ -12013,7 +12023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>164</v>
       </c>
@@ -12027,7 +12037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
@@ -12041,7 +12051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -12055,7 +12065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -12069,7 +12079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
@@ -12083,7 +12093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
@@ -12097,7 +12107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
@@ -12111,7 +12121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
@@ -12125,7 +12135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
@@ -12139,7 +12149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
@@ -12153,7 +12163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
@@ -12167,7 +12177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>45</v>
       </c>
@@ -12181,7 +12191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
@@ -12195,7 +12205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
@@ -12209,7 +12219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
@@ -12223,7 +12233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
@@ -12237,7 +12247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>50</v>
       </c>
@@ -12251,7 +12261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
@@ -12265,7 +12275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>52</v>
       </c>
@@ -12279,7 +12289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
@@ -12293,7 +12303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
@@ -12307,7 +12317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>55</v>
       </c>

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\German\Documents\sebamarapp\backend\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243BC3EC-D48F-4816-B0D0-782664B379D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57120DDC-16E1-4A38-B169-680F689B46F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="939" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="939" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>
@@ -1258,7 +1258,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>26195</v>
+        <v>26000</v>
       </c>
       <c r="C2" s="1">
         <v>7179</v>
@@ -4794,13 +4794,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>36118</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -4886,8 +4886,9 @@
       <c r="I3" s="1">
         <v>41278</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -4916,7 +4917,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -4945,7 +4946,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -4974,7 +4975,7 @@
         <v>59337</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -5003,7 +5004,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -5032,7 +5033,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -5061,7 +5062,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -5090,7 +5091,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -5119,7 +5120,7 @@
         <v>56757</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -5148,7 +5149,7 @@
         <v>61916</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -5177,7 +5178,7 @@
         <v>69656</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -5206,7 +5207,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -5235,7 +5236,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\German\Documents\sebamarapp\backend\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57120DDC-16E1-4A38-B169-680F689B46F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C974BA-FD53-48C5-8805-2FD080D941A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="939" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1258,7 +1258,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>26000</v>
+        <v>26195</v>
       </c>
       <c r="C2" s="1">
         <v>7179</v>
@@ -2177,6 +2177,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\German\Documents\sebamarapp\backend\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sebamarcotizador\backend\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C974BA-FD53-48C5-8805-2FD080D941A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="939" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>
@@ -28,7 +27,7 @@
     <sheet name="SUPERFICIES" sheetId="13" r:id="rId13"/>
     <sheet name="COLORES" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -898,7 +897,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1229,14 +1228,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.3984375" style="1"/>
+    <col min="1" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,12 +1252,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>26195</v>
+        <v>22500</v>
       </c>
       <c r="C2" s="1">
         <v>7179</v>
@@ -1270,7 +1269,7 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1287,7 +1286,7 @@
         <v>3784</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1304,7 +1303,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,7 +1320,7 @@
         <v>5959</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1338,7 +1337,7 @@
         <v>7568</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1355,7 +1354,7 @@
         <v>9197</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1372,7 +1371,7 @@
         <v>10278</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1389,7 +1388,7 @@
         <v>4509</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1406,7 +1405,7 @@
         <v>6309</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1423,7 +1422,7 @@
         <v>8115</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1440,7 +1439,7 @@
         <v>9915</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1457,7 +1456,7 @@
         <v>12625</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1474,7 +1473,7 @@
         <v>15328</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1491,7 +1490,7 @@
         <v>17127</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1508,7 +1507,7 @@
         <v>11359</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1525,7 +1524,7 @@
         <v>13884</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1542,7 +1541,7 @@
         <v>17668</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1559,7 +1558,7 @@
         <v>21459</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1576,7 +1575,7 @@
         <v>23977</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -1593,7 +1592,7 @@
         <v>14603</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,7 +1609,7 @@
         <v>17853</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -1627,7 +1626,7 @@
         <v>22718</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1644,7 +1643,7 @@
         <v>27583</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1661,7 +1660,7 @@
         <v>30833</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,7 +1677,7 @@
         <v>34077</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -1695,7 +1694,7 @@
         <v>37320</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -1712,7 +1711,7 @@
         <v>16231</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -1729,7 +1728,7 @@
         <v>19830</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -1746,7 +1745,7 @@
         <v>25243</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1763,7 +1762,7 @@
         <v>30655</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>163</v>
       </c>
@@ -1780,7 +1779,7 @@
         <v>37861</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>164</v>
       </c>
@@ -1797,7 +1796,7 @@
         <v>41467</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -1814,7 +1813,7 @@
         <v>17853</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -1831,7 +1830,7 @@
         <v>21815</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -1848,7 +1847,7 @@
         <v>27768</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -1865,7 +1864,7 @@
         <v>33714</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -1882,7 +1881,7 @@
         <v>37683</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -1899,7 +1898,7 @@
         <v>41652</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>22718</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -1950,7 +1949,7 @@
         <v>27768</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -1967,7 +1966,7 @@
         <v>35336</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -1984,7 +1983,7 @@
         <v>42911</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -2001,7 +2000,7 @@
         <v>47961</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -2018,7 +2017,7 @@
         <v>53004</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -2035,7 +2034,7 @@
         <v>58060</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -2052,7 +2051,7 @@
         <v>30833</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
@@ -2069,7 +2068,7 @@
         <v>37683</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -2086,7 +2085,7 @@
         <v>50486</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -2103,7 +2102,7 @@
         <v>61304</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -2120,7 +2119,7 @@
         <v>68516</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>75729</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -2154,7 +2153,7 @@
         <v>82941</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -2182,11 +2181,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>165</v>
       </c>
@@ -2206,7 +2205,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>168</v>
       </c>
@@ -2226,7 +2225,7 @@
         <v>61992</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>168</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>69741</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>168</v>
       </c>
@@ -2266,7 +2265,7 @@
         <v>77490</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -2286,7 +2285,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>168</v>
       </c>
@@ -2306,7 +2305,7 @@
         <v>67158</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>168</v>
       </c>
@@ -2326,7 +2325,7 @@
         <v>72324</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>168</v>
       </c>
@@ -2346,7 +2345,7 @@
         <v>80073</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>168</v>
       </c>
@@ -2366,7 +2365,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>168</v>
       </c>
@@ -2386,7 +2385,7 @@
         <v>92988</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>168</v>
       </c>
@@ -2406,7 +2405,7 @@
         <v>77490</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>168</v>
       </c>
@@ -2426,7 +2425,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>168</v>
       </c>
@@ -2446,7 +2445,7 @@
         <v>90405</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -2466,7 +2465,7 @@
         <v>98154</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>168</v>
       </c>
@@ -2486,7 +2485,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>168</v>
       </c>
@@ -2506,7 +2505,7 @@
         <v>82656</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>168</v>
       </c>
@@ -2526,7 +2525,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>168</v>
       </c>
@@ -2546,7 +2545,7 @@
         <v>95571</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>168</v>
       </c>
@@ -2566,7 +2565,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -2586,7 +2585,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>168</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>87822</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>168</v>
       </c>
@@ -2626,7 +2625,7 @@
         <v>92988</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -2646,7 +2645,7 @@
         <v>100737</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>168</v>
       </c>
@@ -2666,7 +2665,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>168</v>
       </c>
@@ -2686,7 +2685,7 @@
         <v>113652</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>168</v>
       </c>
@@ -2706,7 +2705,7 @@
         <v>103320</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>168</v>
       </c>
@@ -2726,7 +2725,7 @@
         <v>108486</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>168</v>
       </c>
@@ -2746,7 +2745,7 @@
         <v>116235</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>168</v>
       </c>
@@ -2766,7 +2765,7 @@
         <v>123984</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>168</v>
       </c>
@@ -2786,7 +2785,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>169</v>
       </c>
@@ -2806,7 +2805,7 @@
         <v>98154</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>169</v>
       </c>
@@ -2826,7 +2825,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>169</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>136899</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>169</v>
       </c>
@@ -2872,11 +2871,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2884,7 +2883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -2892,7 +2891,7 @@
         <v>11094</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -2900,7 +2899,7 @@
         <v>12830</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -2908,7 +2907,7 @@
         <v>14565</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -2916,7 +2915,7 @@
         <v>16300</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>171</v>
       </c>
@@ -2924,7 +2923,7 @@
         <v>18905</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>172</v>
       </c>
@@ -2932,7 +2931,7 @@
         <v>21508</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>173</v>
       </c>
@@ -2940,7 +2939,7 @@
         <v>23244</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -2948,7 +2947,7 @@
         <v>17580</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2956,7 +2955,7 @@
         <v>19772</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2964,7 +2963,7 @@
         <v>21965</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2972,7 +2971,7 @@
         <v>25254</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -2980,7 +2979,7 @@
         <v>28542</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2988,7 +2987,7 @@
         <v>30736</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>174</v>
       </c>
@@ -2996,7 +2995,7 @@
         <v>32927</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>175</v>
       </c>
@@ -3004,7 +3003,7 @@
         <v>35120</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -3012,7 +3011,7 @@
         <v>21508</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>156</v>
       </c>
@@ -3020,7 +3019,7 @@
         <v>23853</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>157</v>
       </c>
@@ -3028,7 +3027,7 @@
         <v>27371</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>158</v>
       </c>
@@ -3036,7 +3035,7 @@
         <v>30887</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>159</v>
       </c>
@@ -3044,7 +3043,7 @@
         <v>33232</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>160</v>
       </c>
@@ -3052,7 +3051,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>161</v>
       </c>
@@ -3060,7 +3059,7 @@
         <v>37923</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>24980</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>27630</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3084,7 +3083,7 @@
         <v>31603</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v>35578</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>162</v>
       </c>
@@ -3100,7 +3099,7 @@
         <v>38227</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>163</v>
       </c>
@@ -3108,7 +3107,7 @@
         <v>40877</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>164</v>
       </c>
@@ -3116,7 +3115,7 @@
         <v>43526</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>176</v>
       </c>
@@ -3124,7 +3123,7 @@
         <v>31405</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -3132,7 +3131,7 @@
         <v>35836</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>178</v>
       </c>
@@ -3140,7 +3139,7 @@
         <v>40268</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -3148,7 +3147,7 @@
         <v>43221</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>180</v>
       </c>
@@ -3156,7 +3155,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>181</v>
       </c>
@@ -3164,7 +3163,7 @@
         <v>49130</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -3172,7 +3171,7 @@
         <v>32982</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -3180,7 +3179,7 @@
         <v>37565</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -3188,7 +3187,7 @@
         <v>42148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -3196,7 +3195,7 @@
         <v>45203</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -3204,7 +3203,7 @@
         <v>48257</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -3212,7 +3211,7 @@
         <v>51313</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -3220,7 +3219,7 @@
         <v>38292</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>183</v>
       </c>
@@ -3228,7 +3227,7 @@
         <v>43518</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>184</v>
       </c>
@@ -3236,7 +3235,7 @@
         <v>48743</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>185</v>
       </c>
@@ -3244,7 +3243,7 @@
         <v>52226</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>186</v>
       </c>
@@ -3252,7 +3251,7 @@
         <v>55709</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>187</v>
       </c>
@@ -3260,7 +3259,7 @@
         <v>59193</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -3268,7 +3267,7 @@
         <v>41832</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -3276,7 +3275,7 @@
         <v>47486</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>53139</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -3292,7 +3291,7 @@
         <v>56908</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -3300,7 +3299,7 @@
         <v>60677</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -3308,7 +3307,7 @@
         <v>64446</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -3322,16 +3321,16 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="1"/>
+    <col min="1" max="1" width="11.42578125" style="1"/>
     <col min="2" max="2" width="21" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.3984375" style="1"/>
+    <col min="3" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
@@ -3354,7 +3353,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>191</v>
       </c>
@@ -3371,7 +3370,7 @@
         <v>81100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>191</v>
       </c>
@@ -3388,7 +3387,7 @@
         <v>81100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>191</v>
       </c>
@@ -3405,7 +3404,7 @@
         <v>86112</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>191</v>
       </c>
@@ -3422,7 +3421,7 @@
         <v>144100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>191</v>
       </c>
@@ -3439,7 +3438,7 @@
         <v>144100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>191</v>
       </c>
@@ -3456,7 +3455,7 @@
         <v>150350</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>191</v>
       </c>
@@ -3473,7 +3472,7 @@
         <v>251300</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>191</v>
       </c>
@@ -3490,7 +3489,7 @@
         <v>251300</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>191</v>
       </c>
@@ -3507,7 +3506,7 @@
         <v>256250</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>191</v>
       </c>
@@ -3521,7 +3520,7 @@
         <v>79500</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>191</v>
       </c>
@@ -3535,7 +3534,7 @@
         <v>79500</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>191</v>
       </c>
@@ -3549,7 +3548,7 @@
         <v>82600</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>191</v>
       </c>
@@ -3563,7 +3562,7 @@
         <v>163500</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>191</v>
       </c>
@@ -3577,7 +3576,7 @@
         <v>163500</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>191</v>
       </c>
@@ -3591,7 +3590,7 @@
         <v>176500</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>200</v>
       </c>
@@ -3608,7 +3607,7 @@
         <v>228900</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>200</v>
       </c>
@@ -3625,7 +3624,7 @@
         <v>228900</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>200</v>
       </c>
@@ -3642,7 +3641,7 @@
         <v>244500</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>200</v>
       </c>
@@ -3659,7 +3658,7 @@
         <v>271400</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>200</v>
       </c>
@@ -3676,7 +3675,7 @@
         <v>271400</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>200</v>
       </c>
@@ -3693,7 +3692,7 @@
         <v>273400</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>200</v>
       </c>
@@ -3710,7 +3709,7 @@
         <v>355700</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>200</v>
       </c>
@@ -3727,7 +3726,7 @@
         <v>355700</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>200</v>
       </c>
@@ -3744,7 +3743,7 @@
         <v>375600</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>257</v>
       </c>
@@ -3758,7 +3757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>257</v>
       </c>
@@ -3772,7 +3771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>257</v>
       </c>
@@ -3786,7 +3785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>257</v>
       </c>
@@ -3800,7 +3799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>257</v>
       </c>
@@ -3814,7 +3813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>257</v>
       </c>
@@ -3828,7 +3827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>257</v>
       </c>
@@ -3842,7 +3841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>257</v>
       </c>
@@ -3856,7 +3855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>257</v>
       </c>
@@ -3870,7 +3869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>257</v>
       </c>
@@ -3884,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>257</v>
       </c>
@@ -3898,7 +3897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>257</v>
       </c>
@@ -3918,15 +3917,15 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.3984375" customWidth="1"/>
-    <col min="3" max="3" width="20.86328125" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>202</v>
       </c>
@@ -3943,7 +3942,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>206</v>
       </c>
@@ -3956,7 +3955,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>206</v>
       </c>
@@ -3969,7 +3968,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>206</v>
       </c>
@@ -3982,7 +3981,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>206</v>
       </c>
@@ -3995,7 +3994,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>206</v>
       </c>
@@ -4008,7 +4007,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>206</v>
       </c>
@@ -4021,7 +4020,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>218</v>
       </c>
@@ -4035,7 +4034,7 @@
         <v>10685</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>218</v>
       </c>
@@ -4049,7 +4048,7 @@
         <v>18080</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>218</v>
       </c>
@@ -4060,7 +4059,7 @@
         <v>7400</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>218</v>
       </c>
@@ -4071,7 +4070,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>218</v>
       </c>
@@ -4085,7 +4084,7 @@
         <v>13517</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>218</v>
       </c>
@@ -4099,7 +4098,7 @@
         <v>20505</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>218</v>
       </c>
@@ -4110,7 +4109,7 @@
         <v>5905</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>218</v>
       </c>
@@ -4121,7 +4120,7 @@
         <v>18500</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>218</v>
       </c>
@@ -4132,7 +4131,7 @@
         <v>48364</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>218</v>
       </c>
@@ -4146,7 +4145,7 @@
         <v>280585</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>218</v>
       </c>
@@ -4160,7 +4159,7 @@
         <v>346865</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>218</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>30208</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>218</v>
       </c>
@@ -4194,7 +4193,7 @@
         <v>23180</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>218</v>
       </c>
@@ -4211,7 +4210,7 @@
         <v>37410</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>218</v>
       </c>
@@ -4228,7 +4227,7 @@
         <v>28263</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>218</v>
       </c>
@@ -4245,7 +4244,7 @@
         <v>52671</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>218</v>
       </c>
@@ -4262,7 +4261,7 @@
         <v>39099</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>218</v>
       </c>
@@ -4279,7 +4278,7 @@
         <v>188750</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>218</v>
       </c>
@@ -4296,7 +4295,7 @@
         <v>139851</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>218</v>
       </c>
@@ -4313,7 +4312,7 @@
         <v>204007</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>218</v>
       </c>
@@ -4330,7 +4329,7 @@
         <v>155108</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>228</v>
       </c>
@@ -4341,7 +4340,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>228</v>
       </c>
@@ -4352,7 +4351,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>228</v>
       </c>
@@ -4363,7 +4362,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>228</v>
       </c>
@@ -4374,7 +4373,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>228</v>
       </c>
@@ -4385,7 +4384,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>228</v>
       </c>
@@ -4396,7 +4395,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>228</v>
       </c>
@@ -4407,7 +4406,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>236</v>
       </c>
@@ -4418,7 +4417,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>236</v>
       </c>
@@ -4429,7 +4428,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>239</v>
       </c>
@@ -4440,7 +4439,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>239</v>
       </c>
@@ -4451,7 +4450,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>239</v>
       </c>
@@ -4462,7 +4461,7 @@
         <v>850000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>239</v>
       </c>
@@ -4473,7 +4472,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>239</v>
       </c>
@@ -4484,7 +4483,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>239</v>
       </c>
@@ -4495,7 +4494,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>239</v>
       </c>
@@ -4509,7 +4508,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>239</v>
       </c>
@@ -4523,7 +4522,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>239</v>
       </c>
@@ -4534,7 +4533,7 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>239</v>
       </c>
@@ -4548,7 +4547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>239</v>
       </c>
@@ -4562,7 +4561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>247</v>
       </c>
@@ -4573,7 +4572,7 @@
         <v>101970</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>247</v>
       </c>
@@ -4584,7 +4583,7 @@
         <v>112167</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -4595,7 +4594,7 @@
         <v>29500</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -4606,7 +4605,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -4617,7 +4616,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -4628,7 +4627,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -4639,7 +4638,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -4650,7 +4649,7 @@
         <v>67000</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -4661,7 +4660,7 @@
         <v>59000</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -4672,7 +4671,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -4683,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -4694,7 +4693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -4705,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -4716,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -4727,7 +4726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -4744,11 +4743,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>250</v>
       </c>
@@ -4756,7 +4755,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>215</v>
       </c>
@@ -4764,7 +4763,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>252</v>
       </c>
@@ -4772,7 +4771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>253</v>
       </c>
@@ -4780,7 +4779,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>255</v>
       </c>
@@ -4794,14 +4793,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.3984375" style="1"/>
+    <col min="1" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4830,7 +4829,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4859,7 +4858,7 @@
         <v>36118</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -4889,7 +4888,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -4918,7 +4917,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -4947,7 +4946,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -4976,7 +4975,7 @@
         <v>59337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -5005,7 +5004,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -5034,7 +5033,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -5063,7 +5062,7 @@
         <v>46437</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>51597</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -5121,7 +5120,7 @@
         <v>56757</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -5150,7 +5149,7 @@
         <v>61916</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -5179,7 +5178,7 @@
         <v>69656</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -5208,7 +5207,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -5237,7 +5236,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -5266,7 +5265,7 @@
         <v>67076</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -5295,7 +5294,7 @@
         <v>72236</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -5324,7 +5323,7 @@
         <v>79975</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -5353,7 +5352,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -5382,7 +5381,7 @@
         <v>92875</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -5411,7 +5410,7 @@
         <v>77396</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -5440,7 +5439,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -5469,7 +5468,7 @@
         <v>90295</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -5498,7 +5497,7 @@
         <v>98034</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -5527,7 +5526,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -5556,7 +5555,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -5585,7 +5584,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -5614,7 +5613,7 @@
         <v>82555</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -5643,7 +5642,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -5672,7 +5671,7 @@
         <v>95454</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -5701,7 +5700,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>163</v>
       </c>
@@ -5730,7 +5729,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>164</v>
       </c>
@@ -5759,7 +5758,7 @@
         <v>118673</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -5788,7 +5787,7 @@
         <v>87715</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -5817,7 +5816,7 @@
         <v>92875</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -5846,7 +5845,7 @@
         <v>100614</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -5875,7 +5874,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -5904,7 +5903,7 @@
         <v>113513</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -5933,7 +5932,7 @@
         <v>118673</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -5962,7 +5961,7 @@
         <v>123833</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -5991,7 +5990,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -6020,7 +6019,7 @@
         <v>108354</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -6049,7 +6048,7 @@
         <v>116093</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -6078,7 +6077,7 @@
         <v>123833</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -6107,7 +6106,7 @@
         <v>128993</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -6136,7 +6135,7 @@
         <v>134152</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -6165,7 +6164,7 @@
         <v>139312</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -6194,7 +6193,7 @@
         <v>128993</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
@@ -6223,7 +6222,7 @@
         <v>134152</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -6252,7 +6251,7 @@
         <v>141892</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -6281,7 +6280,7 @@
         <v>149631</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -6310,7 +6309,7 @@
         <v>154791</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
@@ -6339,7 +6338,7 @@
         <v>159951</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -6368,7 +6367,7 @@
         <v>165110</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -6412,11 +6411,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6442,7 +6441,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -6468,7 +6467,7 @@
         <v>13413</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -6494,7 +6493,7 @@
         <v>17896</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -6520,7 +6519,7 @@
         <v>22380</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -6546,7 +6545,7 @@
         <v>26863</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6572,7 +6571,7 @@
         <v>31346</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -6598,7 +6597,7 @@
         <v>35830</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6624,7 +6623,7 @@
         <v>40313</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -6650,7 +6649,7 @@
         <v>17896</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -6676,7 +6675,7 @@
         <v>23858</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -6702,7 +6701,7 @@
         <v>29819</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -6728,7 +6727,7 @@
         <v>35781</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -6754,7 +6753,7 @@
         <v>41742</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -6780,7 +6779,7 @@
         <v>47703</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -6806,7 +6805,7 @@
         <v>53665</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -6832,7 +6831,7 @@
         <v>22380</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -6858,7 +6857,7 @@
         <v>29819</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -6884,7 +6883,7 @@
         <v>37259</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -6910,7 +6909,7 @@
         <v>44698</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -6936,7 +6935,7 @@
         <v>52138</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -6962,7 +6961,7 @@
         <v>59577</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -6988,7 +6987,7 @@
         <v>67017</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -7014,7 +7013,7 @@
         <v>26863</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -7040,7 +7039,7 @@
         <v>35781</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -7066,7 +7065,7 @@
         <v>44698</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -7092,7 +7091,7 @@
         <v>53616</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -7118,7 +7117,7 @@
         <v>62534</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -7144,7 +7143,7 @@
         <v>71451</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -7170,7 +7169,7 @@
         <v>80369</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -7196,7 +7195,7 @@
         <v>31346</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -7222,7 +7221,7 @@
         <v>41742</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -7248,7 +7247,7 @@
         <v>62534</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -7274,7 +7273,7 @@
         <v>72930</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -7300,7 +7299,7 @@
         <v>83325</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -7326,7 +7325,7 @@
         <v>93721</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -7352,7 +7351,7 @@
         <v>35830</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -7378,7 +7377,7 @@
         <v>47703</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -7404,7 +7403,7 @@
         <v>59577</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -7430,7 +7429,7 @@
         <v>71451</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -7456,7 +7455,7 @@
         <v>83325</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -7482,7 +7481,7 @@
         <v>95199</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -7508,7 +7507,7 @@
         <v>107073</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -7534,7 +7533,7 @@
         <v>40313</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -7560,7 +7559,7 @@
         <v>53665</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -7586,7 +7585,7 @@
         <v>67017</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -7612,7 +7611,7 @@
         <v>80369</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -7638,7 +7637,7 @@
         <v>93721</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -7664,7 +7663,7 @@
         <v>107073</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -7690,7 +7689,7 @@
         <v>120425</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -7716,7 +7715,7 @@
         <v>44723</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -7742,7 +7741,7 @@
         <v>59639</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -7768,7 +7767,7 @@
         <v>74554</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -7794,7 +7793,7 @@
         <v>89470</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -7820,7 +7819,7 @@
         <v>104386</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -7846,7 +7845,7 @@
         <v>119301</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -7872,7 +7871,7 @@
         <v>134217</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -7898,7 +7897,7 @@
         <v>49194</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -7924,7 +7923,7 @@
         <v>65600</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -7950,7 +7949,7 @@
         <v>82006</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -7976,7 +7975,7 @@
         <v>98412</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -8002,7 +8001,7 @@
         <v>114818</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -8028,7 +8027,7 @@
         <v>131224</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>35</v>
       </c>
@@ -8054,7 +8053,7 @@
         <v>147630</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -8080,7 +8079,7 @@
         <v>62619</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -8106,7 +8105,7 @@
         <v>83484</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -8132,7 +8131,7 @@
         <v>104349</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -8158,7 +8157,7 @@
         <v>125214</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -8184,7 +8183,7 @@
         <v>138383</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -8210,7 +8209,7 @@
         <v>151552</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -8242,11 +8241,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8275,7 +8274,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -8304,7 +8303,7 @@
         <v>24806</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -8333,7 +8332,7 @@
         <v>27907</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -8362,7 +8361,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -8391,7 +8390,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -8420,7 +8419,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -8449,7 +8448,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -8478,7 +8477,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -8507,7 +8506,7 @@
         <v>27907</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -8536,7 +8535,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -8565,7 +8564,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -8594,7 +8593,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -8623,7 +8622,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -8652,7 +8651,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -8681,7 +8680,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -8710,7 +8709,7 @@
         <v>31008</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -8739,7 +8738,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -8768,7 +8767,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -8797,7 +8796,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -8826,7 +8825,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -8855,7 +8854,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -8884,7 +8883,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -8913,7 +8912,7 @@
         <v>34109</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -8942,7 +8941,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -8971,7 +8970,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -9000,7 +8999,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -9029,7 +9028,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -9058,7 +9057,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -9087,7 +9086,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -9116,7 +9115,7 @@
         <v>37210</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -9145,7 +9144,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -9174,7 +9173,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -9203,7 +9202,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -9232,7 +9231,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -9261,7 +9260,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -9290,7 +9289,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -9319,7 +9318,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -9348,7 +9347,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -9377,7 +9376,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -9406,7 +9405,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -9435,7 +9434,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -9464,7 +9463,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -9493,7 +9492,7 @@
         <v>43411</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -9522,7 +9521,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -9551,7 +9550,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -9580,7 +9579,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -9609,7 +9608,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -9638,7 +9637,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -9667,7 +9666,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -9696,7 +9695,7 @@
         <v>46512</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -9725,7 +9724,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -9754,7 +9753,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -9783,7 +9782,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -9812,7 +9811,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -9841,7 +9840,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -9870,7 +9869,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>49613</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -9928,7 +9927,7 @@
         <v>52714</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -9957,7 +9956,7 @@
         <v>55814</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -9986,7 +9985,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -10015,7 +10014,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -10044,7 +10043,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>35</v>
       </c>
@@ -10073,7 +10072,7 @@
         <v>68218</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -10102,7 +10101,7 @@
         <v>58915</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -10131,7 +10130,7 @@
         <v>62016</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -10160,7 +10159,7 @@
         <v>65117</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -10189,7 +10188,7 @@
         <v>68218</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -10218,7 +10217,7 @@
         <v>71318</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -10247,7 +10246,7 @@
         <v>74419</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -10282,11 +10281,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -10312,7 +10311,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -10338,7 +10337,7 @@
         <v>115033</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -10364,7 +10363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -10390,7 +10389,7 @@
         <v>83034</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -10416,7 +10415,7 @@
         <v>41517</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -10442,7 +10441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -10468,7 +10467,7 @@
         <v>23064</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -10494,7 +10493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -10520,7 +10519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -10546,7 +10545,7 @@
         <v>41517</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -10572,7 +10571,7 @@
         <v>23064</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -10598,7 +10597,7 @@
         <v>92257</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -10624,7 +10623,7 @@
         <v>29219</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -10650,7 +10649,7 @@
         <v>18446</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -10676,7 +10675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -10702,7 +10701,7 @@
         <v>69199</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -10728,7 +10727,7 @@
         <v>69199</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>141</v>
       </c>
@@ -10754,7 +10753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>142</v>
       </c>
@@ -10786,11 +10785,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -10810,7 +10809,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>143</v>
       </c>
@@ -10830,7 +10829,7 @@
         <v>51329</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -10850,7 +10849,7 @@
         <v>51329</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -10870,7 +10869,7 @@
         <v>40524</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -10890,7 +10889,7 @@
         <v>40524</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>147</v>
       </c>
@@ -10910,7 +10909,7 @@
         <v>27014</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -10930,7 +10929,7 @@
         <v>27014</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -10950,7 +10949,7 @@
         <v>67537</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -10976,11 +10975,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -11009,7 +11008,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -11038,7 +11037,7 @@
         <v>70560</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -11067,7 +11066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -11096,7 +11095,7 @@
         <v>90720</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -11125,7 +11124,7 @@
         <v>45360</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -11154,7 +11153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -11183,7 +11182,7 @@
         <v>32760</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -11212,7 +11211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -11241,7 +11240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -11270,7 +11269,7 @@
         <v>95760</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -11299,7 +11298,7 @@
         <v>57960</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -11328,7 +11327,7 @@
         <v>131040</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -11357,7 +11356,7 @@
         <v>59220</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -11386,7 +11385,7 @@
         <v>34020</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -11415,7 +11414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -11444,7 +11443,7 @@
         <v>133560</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -11473,7 +11472,7 @@
         <v>57960</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -11508,11 +11507,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -11529,7 +11528,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -11546,7 +11545,7 @@
         <v>29689</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -11563,7 +11562,7 @@
         <v>29689</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -11580,7 +11579,7 @@
         <v>14062</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>152</v>
       </c>
@@ -11597,7 +11596,7 @@
         <v>14062</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -11614,7 +11613,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -11631,7 +11630,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -11654,14 +11653,14 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.3984375" style="1"/>
+    <col min="1" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11675,7 +11674,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -11689,7 +11688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -11703,7 +11702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -11717,7 +11716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -11731,7 +11730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -11745,7 +11744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>97</v>
       </c>
@@ -11759,7 +11758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>156</v>
       </c>
@@ -11773,7 +11772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>157</v>
       </c>
@@ -11787,7 +11786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>158</v>
       </c>
@@ -11801,7 +11800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>159</v>
       </c>
@@ -11815,7 +11814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>160</v>
       </c>
@@ -11829,7 +11828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>161</v>
       </c>
@@ -11843,7 +11842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -11857,7 +11856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -11871,7 +11870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -11885,7 +11884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -11899,7 +11898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
@@ -11913,7 +11912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -11927,7 +11926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -11941,7 +11940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -11955,7 +11954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -11969,7 +11968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -11983,7 +11982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -11997,7 +11996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>162</v>
       </c>
@@ -12011,7 +12010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>163</v>
       </c>
@@ -12025,7 +12024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>164</v>
       </c>
@@ -12039,7 +12038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
@@ -12053,7 +12052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -12067,7 +12066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -12081,7 +12080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
@@ -12095,7 +12094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
@@ -12109,7 +12108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
@@ -12123,7 +12122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
@@ -12137,7 +12136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
@@ -12151,7 +12150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
@@ -12165,7 +12164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
@@ -12179,7 +12178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>45</v>
       </c>
@@ -12193,7 +12192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
@@ -12207,7 +12206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
@@ -12221,7 +12220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
@@ -12235,7 +12234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
@@ -12249,7 +12248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>50</v>
       </c>
@@ -12263,7 +12262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
@@ -12277,7 +12276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>52</v>
       </c>
@@ -12291,7 +12290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
@@ -12305,7 +12304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
@@ -12319,7 +12318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>55</v>
       </c>

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939" firstSheet="1" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>

--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -3364,10 +3364,10 @@
         <v>193</v>
       </c>
       <c r="D2" s="1">
-        <v>76300</v>
+        <v>80200</v>
       </c>
       <c r="E2" s="1">
-        <v>81100</v>
+        <v>85200</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3381,10 +3381,10 @@
         <v>194</v>
       </c>
       <c r="D3" s="1">
-        <v>76300</v>
+        <v>80200</v>
       </c>
       <c r="E3" s="1">
-        <v>81100</v>
+        <v>85200</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3398,10 +3398,10 @@
         <v>195</v>
       </c>
       <c r="D4" s="1">
-        <v>81100</v>
+        <v>85200</v>
       </c>
       <c r="E4" s="1">
-        <v>86112</v>
+        <v>90420</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3517,7 +3517,7 @@
         <v>193</v>
       </c>
       <c r="F11" s="1">
-        <v>79500</v>
+        <v>83500</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3531,7 +3531,7 @@
         <v>194</v>
       </c>
       <c r="F12" s="1">
-        <v>79500</v>
+        <v>83500</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3545,7 +3545,7 @@
         <v>195</v>
       </c>
       <c r="F13" s="1">
-        <v>82600</v>
+        <v>86730</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3601,10 +3601,10 @@
         <v>193</v>
       </c>
       <c r="D17" s="1">
-        <v>228900</v>
+        <v>240345</v>
       </c>
       <c r="E17" s="1">
-        <v>228900</v>
+        <v>240345</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3618,10 +3618,10 @@
         <v>194</v>
       </c>
       <c r="D18" s="1">
-        <v>228900</v>
+        <v>240345</v>
       </c>
       <c r="E18" s="1">
-        <v>228900</v>
+        <v>240345</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3635,10 +3635,10 @@
         <v>195</v>
       </c>
       <c r="D19" s="1">
-        <v>244500</v>
+        <v>256725</v>
       </c>
       <c r="E19" s="1">
-        <v>244500</v>
+        <v>256725</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
